--- a/Data/master.xlsx
+++ b/Data/master.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\dev\tools\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF5DCFCA-1DB8-495B-8AEB-73F49C21A969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C56BB37-ECEA-497B-8BEA-6F601F2F7415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1872" yWindow="1872" windowWidth="13020" windowHeight="9180" firstSheet="1" activeTab="3" xr2:uid="{4720D4C3-331B-4002-AC0D-7EA9705E4D1F}"/>
+    <workbookView xWindow="1872" yWindow="1872" windowWidth="13020" windowHeight="9180" firstSheet="2" activeTab="4" xr2:uid="{28D3F2F5-2DFF-41DF-B243-6C4AAE3F1CC0}"/>
   </bookViews>
   <sheets>
     <sheet name="contacts" sheetId="1" r:id="rId1"/>
     <sheet name="bookmarks" sheetId="2" r:id="rId2"/>
     <sheet name="folders" sheetId="3" r:id="rId3"/>
     <sheet name="products" sheetId="4" r:id="rId4"/>
+    <sheet name="employees" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1161">
   <si>
     <t>name</t>
   </si>
@@ -169,6 +170,3357 @@
   </si>
   <si>
     <t>完成品</t>
+  </si>
+  <si>
+    <t>employee_id</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>department_name</t>
+  </si>
+  <si>
+    <t>position_title</t>
+  </si>
+  <si>
+    <t>email_address</t>
+  </si>
+  <si>
+    <t>phone_number</t>
+  </si>
+  <si>
+    <t>hire_date</t>
+  </si>
+  <si>
+    <t>monthly_salary</t>
+  </si>
+  <si>
+    <t>document_folder_path</t>
+  </si>
+  <si>
+    <t>intranet_profile_url</t>
+  </si>
+  <si>
+    <t>E0001</t>
+  </si>
+  <si>
+    <t>部長</t>
+  </si>
+  <si>
+    <t>emp0001@example.com</t>
+  </si>
+  <si>
+    <t>03-1000-5000</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0001</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0001</t>
+  </si>
+  <si>
+    <t>E0002</t>
+  </si>
+  <si>
+    <t>鈴木太郎</t>
+  </si>
+  <si>
+    <t>課長</t>
+  </si>
+  <si>
+    <t>emp0002@example.com</t>
+  </si>
+  <si>
+    <t>03-1001-5001</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0002</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0002</t>
+  </si>
+  <si>
+    <t>E0003</t>
+  </si>
+  <si>
+    <t>佐藤太郎</t>
+  </si>
+  <si>
+    <t>係長</t>
+  </si>
+  <si>
+    <t>emp0003@example.com</t>
+  </si>
+  <si>
+    <t>03-1002-5002</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0003</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0003</t>
+  </si>
+  <si>
+    <t>E0004</t>
+  </si>
+  <si>
+    <t>高橋太郎</t>
+  </si>
+  <si>
+    <t>企画部</t>
+  </si>
+  <si>
+    <t>主任</t>
+  </si>
+  <si>
+    <t>emp0004@example.com</t>
+  </si>
+  <si>
+    <t>03-1003-5003</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0004</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0004</t>
+  </si>
+  <si>
+    <t>E0005</t>
+  </si>
+  <si>
+    <t>渡辺太郎</t>
+  </si>
+  <si>
+    <t>経理部</t>
+  </si>
+  <si>
+    <t>一般</t>
+  </si>
+  <si>
+    <t>emp0005@example.com</t>
+  </si>
+  <si>
+    <t>03-1004-5004</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0005</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0005</t>
+  </si>
+  <si>
+    <t>E0006</t>
+  </si>
+  <si>
+    <t>伊藤太郎</t>
+  </si>
+  <si>
+    <t>人事部</t>
+  </si>
+  <si>
+    <t>emp0006@example.com</t>
+  </si>
+  <si>
+    <t>03-1005-5005</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0006</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0006</t>
+  </si>
+  <si>
+    <t>E0007</t>
+  </si>
+  <si>
+    <t>山本太郎</t>
+  </si>
+  <si>
+    <t>広報部</t>
+  </si>
+  <si>
+    <t>emp0007@example.com</t>
+  </si>
+  <si>
+    <t>03-1006-5006</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0007</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0007</t>
+  </si>
+  <si>
+    <t>E0008</t>
+  </si>
+  <si>
+    <t>中村太郎</t>
+  </si>
+  <si>
+    <t>法務部</t>
+  </si>
+  <si>
+    <t>emp0008@example.com</t>
+  </si>
+  <si>
+    <t>03-1007-5007</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0008</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0008</t>
+  </si>
+  <si>
+    <t>E0009</t>
+  </si>
+  <si>
+    <t>小林太郎</t>
+  </si>
+  <si>
+    <t>emp0009@example.com</t>
+  </si>
+  <si>
+    <t>03-1008-5008</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0009</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0009</t>
+  </si>
+  <si>
+    <t>E0010</t>
+  </si>
+  <si>
+    <t>加藤太郎</t>
+  </si>
+  <si>
+    <t>emp0010@example.com</t>
+  </si>
+  <si>
+    <t>03-1009-5009</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0010</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0010</t>
+  </si>
+  <si>
+    <t>E0011</t>
+  </si>
+  <si>
+    <t>田中花子</t>
+  </si>
+  <si>
+    <t>emp0011@example.com</t>
+  </si>
+  <si>
+    <t>03-1010-5010</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0011</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0011</t>
+  </si>
+  <si>
+    <t>E0012</t>
+  </si>
+  <si>
+    <t>emp0012@example.com</t>
+  </si>
+  <si>
+    <t>03-1011-5011</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0012</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0012</t>
+  </si>
+  <si>
+    <t>E0013</t>
+  </si>
+  <si>
+    <t>佐藤花子</t>
+  </si>
+  <si>
+    <t>emp0013@example.com</t>
+  </si>
+  <si>
+    <t>03-1012-5012</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0013</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0013</t>
+  </si>
+  <si>
+    <t>E0014</t>
+  </si>
+  <si>
+    <t>高橋花子</t>
+  </si>
+  <si>
+    <t>emp0014@example.com</t>
+  </si>
+  <si>
+    <t>03-1013-5013</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0014</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0014</t>
+  </si>
+  <si>
+    <t>E0015</t>
+  </si>
+  <si>
+    <t>渡辺花子</t>
+  </si>
+  <si>
+    <t>emp0015@example.com</t>
+  </si>
+  <si>
+    <t>03-1014-5014</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0015</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0015</t>
+  </si>
+  <si>
+    <t>E0016</t>
+  </si>
+  <si>
+    <t>伊藤花子</t>
+  </si>
+  <si>
+    <t>emp0016@example.com</t>
+  </si>
+  <si>
+    <t>03-1015-5015</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0016</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0016</t>
+  </si>
+  <si>
+    <t>E0017</t>
+  </si>
+  <si>
+    <t>山本花子</t>
+  </si>
+  <si>
+    <t>emp0017@example.com</t>
+  </si>
+  <si>
+    <t>03-1016-5016</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0017</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0017</t>
+  </si>
+  <si>
+    <t>E0018</t>
+  </si>
+  <si>
+    <t>中村花子</t>
+  </si>
+  <si>
+    <t>emp0018@example.com</t>
+  </si>
+  <si>
+    <t>03-1017-5017</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0018</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0018</t>
+  </si>
+  <si>
+    <t>E0019</t>
+  </si>
+  <si>
+    <t>小林花子</t>
+  </si>
+  <si>
+    <t>emp0019@example.com</t>
+  </si>
+  <si>
+    <t>03-1018-5018</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0019</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0019</t>
+  </si>
+  <si>
+    <t>E0020</t>
+  </si>
+  <si>
+    <t>加藤花子</t>
+  </si>
+  <si>
+    <t>emp0020@example.com</t>
+  </si>
+  <si>
+    <t>03-1019-5019</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0020</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0020</t>
+  </si>
+  <si>
+    <t>E0021</t>
+  </si>
+  <si>
+    <t>田中一郎</t>
+  </si>
+  <si>
+    <t>emp0021@example.com</t>
+  </si>
+  <si>
+    <t>03-1020-5020</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0021</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0021</t>
+  </si>
+  <si>
+    <t>E0022</t>
+  </si>
+  <si>
+    <t>鈴木一郎</t>
+  </si>
+  <si>
+    <t>emp0022@example.com</t>
+  </si>
+  <si>
+    <t>03-1021-5021</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0022</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0022</t>
+  </si>
+  <si>
+    <t>E0023</t>
+  </si>
+  <si>
+    <t>emp0023@example.com</t>
+  </si>
+  <si>
+    <t>03-1022-5022</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0023</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0023</t>
+  </si>
+  <si>
+    <t>E0024</t>
+  </si>
+  <si>
+    <t>高橋一郎</t>
+  </si>
+  <si>
+    <t>emp0024@example.com</t>
+  </si>
+  <si>
+    <t>03-1023-5023</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0024</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0024</t>
+  </si>
+  <si>
+    <t>E0025</t>
+  </si>
+  <si>
+    <t>渡辺一郎</t>
+  </si>
+  <si>
+    <t>emp0025@example.com</t>
+  </si>
+  <si>
+    <t>03-1024-5024</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0025</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0025</t>
+  </si>
+  <si>
+    <t>E0026</t>
+  </si>
+  <si>
+    <t>伊藤一郎</t>
+  </si>
+  <si>
+    <t>emp0026@example.com</t>
+  </si>
+  <si>
+    <t>03-1025-5025</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0026</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0026</t>
+  </si>
+  <si>
+    <t>E0027</t>
+  </si>
+  <si>
+    <t>山本一郎</t>
+  </si>
+  <si>
+    <t>emp0027@example.com</t>
+  </si>
+  <si>
+    <t>03-1026-5026</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0027</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0027</t>
+  </si>
+  <si>
+    <t>E0028</t>
+  </si>
+  <si>
+    <t>中村一郎</t>
+  </si>
+  <si>
+    <t>emp0028@example.com</t>
+  </si>
+  <si>
+    <t>03-1027-5027</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0028</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0028</t>
+  </si>
+  <si>
+    <t>E0029</t>
+  </si>
+  <si>
+    <t>小林一郎</t>
+  </si>
+  <si>
+    <t>emp0029@example.com</t>
+  </si>
+  <si>
+    <t>03-1028-5028</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0029</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0029</t>
+  </si>
+  <si>
+    <t>E0030</t>
+  </si>
+  <si>
+    <t>加藤一郎</t>
+  </si>
+  <si>
+    <t>emp0030@example.com</t>
+  </si>
+  <si>
+    <t>03-1029-5029</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0030</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0030</t>
+  </si>
+  <si>
+    <t>E0031</t>
+  </si>
+  <si>
+    <t>田中美咲</t>
+  </si>
+  <si>
+    <t>emp0031@example.com</t>
+  </si>
+  <si>
+    <t>03-1030-5030</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0031</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0031</t>
+  </si>
+  <si>
+    <t>E0032</t>
+  </si>
+  <si>
+    <t>鈴木美咲</t>
+  </si>
+  <si>
+    <t>emp0032@example.com</t>
+  </si>
+  <si>
+    <t>03-1031-5031</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0032</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0032</t>
+  </si>
+  <si>
+    <t>E0033</t>
+  </si>
+  <si>
+    <t>佐藤美咲</t>
+  </si>
+  <si>
+    <t>emp0033@example.com</t>
+  </si>
+  <si>
+    <t>03-1032-5032</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0033</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0033</t>
+  </si>
+  <si>
+    <t>E0034</t>
+  </si>
+  <si>
+    <t>高橋美咲</t>
+  </si>
+  <si>
+    <t>emp0034@example.com</t>
+  </si>
+  <si>
+    <t>03-1033-5033</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0034</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0034</t>
+  </si>
+  <si>
+    <t>E0035</t>
+  </si>
+  <si>
+    <t>渡辺美咲</t>
+  </si>
+  <si>
+    <t>emp0035@example.com</t>
+  </si>
+  <si>
+    <t>03-1034-5034</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0035</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0035</t>
+  </si>
+  <si>
+    <t>E0036</t>
+  </si>
+  <si>
+    <t>伊藤美咲</t>
+  </si>
+  <si>
+    <t>emp0036@example.com</t>
+  </si>
+  <si>
+    <t>03-1035-5035</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0036</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0036</t>
+  </si>
+  <si>
+    <t>E0037</t>
+  </si>
+  <si>
+    <t>山本美咲</t>
+  </si>
+  <si>
+    <t>emp0037@example.com</t>
+  </si>
+  <si>
+    <t>03-1036-5036</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0037</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0037</t>
+  </si>
+  <si>
+    <t>E0038</t>
+  </si>
+  <si>
+    <t>中村美咲</t>
+  </si>
+  <si>
+    <t>emp0038@example.com</t>
+  </si>
+  <si>
+    <t>03-1037-5037</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0038</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0038</t>
+  </si>
+  <si>
+    <t>E0039</t>
+  </si>
+  <si>
+    <t>小林美咲</t>
+  </si>
+  <si>
+    <t>emp0039@example.com</t>
+  </si>
+  <si>
+    <t>03-1038-5038</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0039</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0039</t>
+  </si>
+  <si>
+    <t>E0040</t>
+  </si>
+  <si>
+    <t>加藤美咲</t>
+  </si>
+  <si>
+    <t>emp0040@example.com</t>
+  </si>
+  <si>
+    <t>03-1039-5039</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0040</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0040</t>
+  </si>
+  <si>
+    <t>E0041</t>
+  </si>
+  <si>
+    <t>田中健太</t>
+  </si>
+  <si>
+    <t>emp0041@example.com</t>
+  </si>
+  <si>
+    <t>03-1040-5040</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0041</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0041</t>
+  </si>
+  <si>
+    <t>E0042</t>
+  </si>
+  <si>
+    <t>鈴木健太</t>
+  </si>
+  <si>
+    <t>emp0042@example.com</t>
+  </si>
+  <si>
+    <t>03-1041-5041</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0042</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0042</t>
+  </si>
+  <si>
+    <t>E0043</t>
+  </si>
+  <si>
+    <t>佐藤健太</t>
+  </si>
+  <si>
+    <t>emp0043@example.com</t>
+  </si>
+  <si>
+    <t>03-1042-5042</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0043</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0043</t>
+  </si>
+  <si>
+    <t>E0044</t>
+  </si>
+  <si>
+    <t>高橋健太</t>
+  </si>
+  <si>
+    <t>emp0044@example.com</t>
+  </si>
+  <si>
+    <t>03-1043-5043</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0044</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0044</t>
+  </si>
+  <si>
+    <t>E0045</t>
+  </si>
+  <si>
+    <t>渡辺健太</t>
+  </si>
+  <si>
+    <t>emp0045@example.com</t>
+  </si>
+  <si>
+    <t>03-1044-5044</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0045</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0045</t>
+  </si>
+  <si>
+    <t>E0046</t>
+  </si>
+  <si>
+    <t>伊藤健太</t>
+  </si>
+  <si>
+    <t>emp0046@example.com</t>
+  </si>
+  <si>
+    <t>03-1045-5045</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0046</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0046</t>
+  </si>
+  <si>
+    <t>E0047</t>
+  </si>
+  <si>
+    <t>山本健太</t>
+  </si>
+  <si>
+    <t>emp0047@example.com</t>
+  </si>
+  <si>
+    <t>03-1046-5046</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0047</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0047</t>
+  </si>
+  <si>
+    <t>E0048</t>
+  </si>
+  <si>
+    <t>中村健太</t>
+  </si>
+  <si>
+    <t>emp0048@example.com</t>
+  </si>
+  <si>
+    <t>03-1047-5047</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0048</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0048</t>
+  </si>
+  <si>
+    <t>E0049</t>
+  </si>
+  <si>
+    <t>小林健太</t>
+  </si>
+  <si>
+    <t>emp0049@example.com</t>
+  </si>
+  <si>
+    <t>03-1048-5048</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0049</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0049</t>
+  </si>
+  <si>
+    <t>E0050</t>
+  </si>
+  <si>
+    <t>加藤健太</t>
+  </si>
+  <si>
+    <t>emp0050@example.com</t>
+  </si>
+  <si>
+    <t>03-1049-5049</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0050</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0050</t>
+  </si>
+  <si>
+    <t>E0051</t>
+  </si>
+  <si>
+    <t>田中由美</t>
+  </si>
+  <si>
+    <t>emp0051@example.com</t>
+  </si>
+  <si>
+    <t>03-1050-5050</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0051</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0051</t>
+  </si>
+  <si>
+    <t>E0052</t>
+  </si>
+  <si>
+    <t>鈴木由美</t>
+  </si>
+  <si>
+    <t>emp0052@example.com</t>
+  </si>
+  <si>
+    <t>03-1051-5051</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0052</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0052</t>
+  </si>
+  <si>
+    <t>E0053</t>
+  </si>
+  <si>
+    <t>佐藤由美</t>
+  </si>
+  <si>
+    <t>emp0053@example.com</t>
+  </si>
+  <si>
+    <t>03-1052-5052</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0053</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0053</t>
+  </si>
+  <si>
+    <t>E0054</t>
+  </si>
+  <si>
+    <t>高橋由美</t>
+  </si>
+  <si>
+    <t>emp0054@example.com</t>
+  </si>
+  <si>
+    <t>03-1053-5053</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0054</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0054</t>
+  </si>
+  <si>
+    <t>E0055</t>
+  </si>
+  <si>
+    <t>渡辺由美</t>
+  </si>
+  <si>
+    <t>emp0055@example.com</t>
+  </si>
+  <si>
+    <t>03-1054-5054</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0055</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0055</t>
+  </si>
+  <si>
+    <t>E0056</t>
+  </si>
+  <si>
+    <t>伊藤由美</t>
+  </si>
+  <si>
+    <t>emp0056@example.com</t>
+  </si>
+  <si>
+    <t>03-1055-5055</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0056</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0056</t>
+  </si>
+  <si>
+    <t>E0057</t>
+  </si>
+  <si>
+    <t>山本由美</t>
+  </si>
+  <si>
+    <t>emp0057@example.com</t>
+  </si>
+  <si>
+    <t>03-1056-5056</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0057</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0057</t>
+  </si>
+  <si>
+    <t>E0058</t>
+  </si>
+  <si>
+    <t>中村由美</t>
+  </si>
+  <si>
+    <t>emp0058@example.com</t>
+  </si>
+  <si>
+    <t>03-1057-5057</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0058</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0058</t>
+  </si>
+  <si>
+    <t>E0059</t>
+  </si>
+  <si>
+    <t>小林由美</t>
+  </si>
+  <si>
+    <t>emp0059@example.com</t>
+  </si>
+  <si>
+    <t>03-1058-5058</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0059</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0059</t>
+  </si>
+  <si>
+    <t>E0060</t>
+  </si>
+  <si>
+    <t>加藤由美</t>
+  </si>
+  <si>
+    <t>emp0060@example.com</t>
+  </si>
+  <si>
+    <t>03-1059-5059</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0060</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0060</t>
+  </si>
+  <si>
+    <t>E0061</t>
+  </si>
+  <si>
+    <t>田中大輔</t>
+  </si>
+  <si>
+    <t>emp0061@example.com</t>
+  </si>
+  <si>
+    <t>03-1060-5060</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0061</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0061</t>
+  </si>
+  <si>
+    <t>E0062</t>
+  </si>
+  <si>
+    <t>鈴木大輔</t>
+  </si>
+  <si>
+    <t>emp0062@example.com</t>
+  </si>
+  <si>
+    <t>03-1061-5061</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0062</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0062</t>
+  </si>
+  <si>
+    <t>E0063</t>
+  </si>
+  <si>
+    <t>佐藤大輔</t>
+  </si>
+  <si>
+    <t>emp0063@example.com</t>
+  </si>
+  <si>
+    <t>03-1062-5062</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0063</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0063</t>
+  </si>
+  <si>
+    <t>E0064</t>
+  </si>
+  <si>
+    <t>高橋大輔</t>
+  </si>
+  <si>
+    <t>emp0064@example.com</t>
+  </si>
+  <si>
+    <t>03-1063-5063</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0064</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0064</t>
+  </si>
+  <si>
+    <t>E0065</t>
+  </si>
+  <si>
+    <t>渡辺大輔</t>
+  </si>
+  <si>
+    <t>emp0065@example.com</t>
+  </si>
+  <si>
+    <t>03-1064-5064</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0065</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0065</t>
+  </si>
+  <si>
+    <t>E0066</t>
+  </si>
+  <si>
+    <t>伊藤大輔</t>
+  </si>
+  <si>
+    <t>emp0066@example.com</t>
+  </si>
+  <si>
+    <t>03-1065-5065</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0066</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0066</t>
+  </si>
+  <si>
+    <t>E0067</t>
+  </si>
+  <si>
+    <t>山本大輔</t>
+  </si>
+  <si>
+    <t>emp0067@example.com</t>
+  </si>
+  <si>
+    <t>03-1066-5066</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0067</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0067</t>
+  </si>
+  <si>
+    <t>E0068</t>
+  </si>
+  <si>
+    <t>中村大輔</t>
+  </si>
+  <si>
+    <t>emp0068@example.com</t>
+  </si>
+  <si>
+    <t>03-1067-5067</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0068</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0068</t>
+  </si>
+  <si>
+    <t>E0069</t>
+  </si>
+  <si>
+    <t>小林大輔</t>
+  </si>
+  <si>
+    <t>emp0069@example.com</t>
+  </si>
+  <si>
+    <t>03-1068-5068</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0069</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0069</t>
+  </si>
+  <si>
+    <t>E0070</t>
+  </si>
+  <si>
+    <t>加藤大輔</t>
+  </si>
+  <si>
+    <t>emp0070@example.com</t>
+  </si>
+  <si>
+    <t>03-1069-5069</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0070</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0070</t>
+  </si>
+  <si>
+    <t>E0071</t>
+  </si>
+  <si>
+    <t>田中恵子</t>
+  </si>
+  <si>
+    <t>emp0071@example.com</t>
+  </si>
+  <si>
+    <t>03-1070-5070</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0071</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0071</t>
+  </si>
+  <si>
+    <t>E0072</t>
+  </si>
+  <si>
+    <t>鈴木恵子</t>
+  </si>
+  <si>
+    <t>emp0072@example.com</t>
+  </si>
+  <si>
+    <t>03-1071-5071</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0072</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0072</t>
+  </si>
+  <si>
+    <t>E0073</t>
+  </si>
+  <si>
+    <t>佐藤恵子</t>
+  </si>
+  <si>
+    <t>emp0073@example.com</t>
+  </si>
+  <si>
+    <t>03-1072-5072</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0073</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0073</t>
+  </si>
+  <si>
+    <t>E0074</t>
+  </si>
+  <si>
+    <t>高橋恵子</t>
+  </si>
+  <si>
+    <t>emp0074@example.com</t>
+  </si>
+  <si>
+    <t>03-1073-5073</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0074</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0074</t>
+  </si>
+  <si>
+    <t>E0075</t>
+  </si>
+  <si>
+    <t>渡辺恵子</t>
+  </si>
+  <si>
+    <t>emp0075@example.com</t>
+  </si>
+  <si>
+    <t>03-1074-5074</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0075</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0075</t>
+  </si>
+  <si>
+    <t>E0076</t>
+  </si>
+  <si>
+    <t>伊藤恵子</t>
+  </si>
+  <si>
+    <t>emp0076@example.com</t>
+  </si>
+  <si>
+    <t>03-1075-5075</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0076</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0076</t>
+  </si>
+  <si>
+    <t>E0077</t>
+  </si>
+  <si>
+    <t>山本恵子</t>
+  </si>
+  <si>
+    <t>emp0077@example.com</t>
+  </si>
+  <si>
+    <t>03-1076-5076</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0077</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0077</t>
+  </si>
+  <si>
+    <t>E0078</t>
+  </si>
+  <si>
+    <t>中村恵子</t>
+  </si>
+  <si>
+    <t>emp0078@example.com</t>
+  </si>
+  <si>
+    <t>03-1077-5077</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0078</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0078</t>
+  </si>
+  <si>
+    <t>E0079</t>
+  </si>
+  <si>
+    <t>小林恵子</t>
+  </si>
+  <si>
+    <t>emp0079@example.com</t>
+  </si>
+  <si>
+    <t>03-1078-5078</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0079</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0079</t>
+  </si>
+  <si>
+    <t>E0080</t>
+  </si>
+  <si>
+    <t>加藤恵子</t>
+  </si>
+  <si>
+    <t>emp0080@example.com</t>
+  </si>
+  <si>
+    <t>03-1079-5079</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0080</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0080</t>
+  </si>
+  <si>
+    <t>E0081</t>
+  </si>
+  <si>
+    <t>田中翔太</t>
+  </si>
+  <si>
+    <t>emp0081@example.com</t>
+  </si>
+  <si>
+    <t>03-1080-5080</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0081</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0081</t>
+  </si>
+  <si>
+    <t>E0082</t>
+  </si>
+  <si>
+    <t>鈴木翔太</t>
+  </si>
+  <si>
+    <t>emp0082@example.com</t>
+  </si>
+  <si>
+    <t>03-1081-5081</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0082</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0082</t>
+  </si>
+  <si>
+    <t>E0083</t>
+  </si>
+  <si>
+    <t>佐藤翔太</t>
+  </si>
+  <si>
+    <t>emp0083@example.com</t>
+  </si>
+  <si>
+    <t>03-1082-5082</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0083</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0083</t>
+  </si>
+  <si>
+    <t>E0084</t>
+  </si>
+  <si>
+    <t>高橋翔太</t>
+  </si>
+  <si>
+    <t>emp0084@example.com</t>
+  </si>
+  <si>
+    <t>03-1083-5083</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0084</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0084</t>
+  </si>
+  <si>
+    <t>E0085</t>
+  </si>
+  <si>
+    <t>渡辺翔太</t>
+  </si>
+  <si>
+    <t>emp0085@example.com</t>
+  </si>
+  <si>
+    <t>03-1084-5084</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0085</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0085</t>
+  </si>
+  <si>
+    <t>E0086</t>
+  </si>
+  <si>
+    <t>伊藤翔太</t>
+  </si>
+  <si>
+    <t>emp0086@example.com</t>
+  </si>
+  <si>
+    <t>03-1085-5085</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0086</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0086</t>
+  </si>
+  <si>
+    <t>E0087</t>
+  </si>
+  <si>
+    <t>山本翔太</t>
+  </si>
+  <si>
+    <t>emp0087@example.com</t>
+  </si>
+  <si>
+    <t>03-1086-5086</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0087</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0087</t>
+  </si>
+  <si>
+    <t>E0088</t>
+  </si>
+  <si>
+    <t>中村翔太</t>
+  </si>
+  <si>
+    <t>emp0088@example.com</t>
+  </si>
+  <si>
+    <t>03-1087-5087</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0088</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0088</t>
+  </si>
+  <si>
+    <t>E0089</t>
+  </si>
+  <si>
+    <t>小林翔太</t>
+  </si>
+  <si>
+    <t>emp0089@example.com</t>
+  </si>
+  <si>
+    <t>03-1088-5088</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0089</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0089</t>
+  </si>
+  <si>
+    <t>E0090</t>
+  </si>
+  <si>
+    <t>加藤翔太</t>
+  </si>
+  <si>
+    <t>emp0090@example.com</t>
+  </si>
+  <si>
+    <t>03-1089-5089</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0090</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0090</t>
+  </si>
+  <si>
+    <t>E0091</t>
+  </si>
+  <si>
+    <t>田中あかり</t>
+  </si>
+  <si>
+    <t>emp0091@example.com</t>
+  </si>
+  <si>
+    <t>03-1090-5090</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0091</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0091</t>
+  </si>
+  <si>
+    <t>E0092</t>
+  </si>
+  <si>
+    <t>鈴木あかり</t>
+  </si>
+  <si>
+    <t>emp0092@example.com</t>
+  </si>
+  <si>
+    <t>03-1091-5091</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0092</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0092</t>
+  </si>
+  <si>
+    <t>E0093</t>
+  </si>
+  <si>
+    <t>佐藤あかり</t>
+  </si>
+  <si>
+    <t>emp0093@example.com</t>
+  </si>
+  <si>
+    <t>03-1092-5092</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0093</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0093</t>
+  </si>
+  <si>
+    <t>E0094</t>
+  </si>
+  <si>
+    <t>高橋あかり</t>
+  </si>
+  <si>
+    <t>emp0094@example.com</t>
+  </si>
+  <si>
+    <t>03-1093-5093</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0094</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0094</t>
+  </si>
+  <si>
+    <t>E0095</t>
+  </si>
+  <si>
+    <t>渡辺あかり</t>
+  </si>
+  <si>
+    <t>emp0095@example.com</t>
+  </si>
+  <si>
+    <t>03-1094-5094</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0095</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0095</t>
+  </si>
+  <si>
+    <t>E0096</t>
+  </si>
+  <si>
+    <t>伊藤あかり</t>
+  </si>
+  <si>
+    <t>emp0096@example.com</t>
+  </si>
+  <si>
+    <t>03-1095-5095</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0096</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0096</t>
+  </si>
+  <si>
+    <t>E0097</t>
+  </si>
+  <si>
+    <t>山本あかり</t>
+  </si>
+  <si>
+    <t>emp0097@example.com</t>
+  </si>
+  <si>
+    <t>03-1096-5096</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0097</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0097</t>
+  </si>
+  <si>
+    <t>E0098</t>
+  </si>
+  <si>
+    <t>中村あかり</t>
+  </si>
+  <si>
+    <t>emp0098@example.com</t>
+  </si>
+  <si>
+    <t>03-1097-5097</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0098</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0098</t>
+  </si>
+  <si>
+    <t>E0099</t>
+  </si>
+  <si>
+    <t>小林あかり</t>
+  </si>
+  <si>
+    <t>emp0099@example.com</t>
+  </si>
+  <si>
+    <t>03-1098-5098</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0099</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0099</t>
+  </si>
+  <si>
+    <t>E0100</t>
+  </si>
+  <si>
+    <t>加藤あかり</t>
+  </si>
+  <si>
+    <t>emp0100@example.com</t>
+  </si>
+  <si>
+    <t>03-1099-5099</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0100</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0100</t>
+  </si>
+  <si>
+    <t>E0101</t>
+  </si>
+  <si>
+    <t>emp0101@example.com</t>
+  </si>
+  <si>
+    <t>03-1100-5100</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0101</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0101</t>
+  </si>
+  <si>
+    <t>E0102</t>
+  </si>
+  <si>
+    <t>emp0102@example.com</t>
+  </si>
+  <si>
+    <t>03-1101-5101</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0102</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0102</t>
+  </si>
+  <si>
+    <t>E0103</t>
+  </si>
+  <si>
+    <t>emp0103@example.com</t>
+  </si>
+  <si>
+    <t>03-1102-5102</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0103</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0103</t>
+  </si>
+  <si>
+    <t>E0104</t>
+  </si>
+  <si>
+    <t>emp0104@example.com</t>
+  </si>
+  <si>
+    <t>03-1103-5103</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0104</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0104</t>
+  </si>
+  <si>
+    <t>E0105</t>
+  </si>
+  <si>
+    <t>emp0105@example.com</t>
+  </si>
+  <si>
+    <t>03-1104-5104</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0105</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0105</t>
+  </si>
+  <si>
+    <t>E0106</t>
+  </si>
+  <si>
+    <t>emp0106@example.com</t>
+  </si>
+  <si>
+    <t>03-1105-5105</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0106</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0106</t>
+  </si>
+  <si>
+    <t>E0107</t>
+  </si>
+  <si>
+    <t>emp0107@example.com</t>
+  </si>
+  <si>
+    <t>03-1106-5106</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0107</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0107</t>
+  </si>
+  <si>
+    <t>E0108</t>
+  </si>
+  <si>
+    <t>emp0108@example.com</t>
+  </si>
+  <si>
+    <t>03-1107-5107</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0108</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0108</t>
+  </si>
+  <si>
+    <t>E0109</t>
+  </si>
+  <si>
+    <t>emp0109@example.com</t>
+  </si>
+  <si>
+    <t>03-1108-5108</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0109</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0109</t>
+  </si>
+  <si>
+    <t>E0110</t>
+  </si>
+  <si>
+    <t>emp0110@example.com</t>
+  </si>
+  <si>
+    <t>03-1109-5109</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0110</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0110</t>
+  </si>
+  <si>
+    <t>E0111</t>
+  </si>
+  <si>
+    <t>emp0111@example.com</t>
+  </si>
+  <si>
+    <t>03-1110-5110</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0111</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0111</t>
+  </si>
+  <si>
+    <t>E0112</t>
+  </si>
+  <si>
+    <t>emp0112@example.com</t>
+  </si>
+  <si>
+    <t>03-1111-5111</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0112</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0112</t>
+  </si>
+  <si>
+    <t>E0113</t>
+  </si>
+  <si>
+    <t>emp0113@example.com</t>
+  </si>
+  <si>
+    <t>03-1112-5112</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0113</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0113</t>
+  </si>
+  <si>
+    <t>E0114</t>
+  </si>
+  <si>
+    <t>emp0114@example.com</t>
+  </si>
+  <si>
+    <t>03-1113-5113</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0114</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0114</t>
+  </si>
+  <si>
+    <t>E0115</t>
+  </si>
+  <si>
+    <t>emp0115@example.com</t>
+  </si>
+  <si>
+    <t>03-1114-5114</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0115</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0115</t>
+  </si>
+  <si>
+    <t>E0116</t>
+  </si>
+  <si>
+    <t>emp0116@example.com</t>
+  </si>
+  <si>
+    <t>03-1115-5115</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0116</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0116</t>
+  </si>
+  <si>
+    <t>E0117</t>
+  </si>
+  <si>
+    <t>emp0117@example.com</t>
+  </si>
+  <si>
+    <t>03-1116-5116</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0117</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0117</t>
+  </si>
+  <si>
+    <t>E0118</t>
+  </si>
+  <si>
+    <t>emp0118@example.com</t>
+  </si>
+  <si>
+    <t>03-1117-5117</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0118</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0118</t>
+  </si>
+  <si>
+    <t>E0119</t>
+  </si>
+  <si>
+    <t>emp0119@example.com</t>
+  </si>
+  <si>
+    <t>03-1118-5118</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0119</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0119</t>
+  </si>
+  <si>
+    <t>E0120</t>
+  </si>
+  <si>
+    <t>emp0120@example.com</t>
+  </si>
+  <si>
+    <t>03-1119-5119</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0120</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0120</t>
+  </si>
+  <si>
+    <t>E0121</t>
+  </si>
+  <si>
+    <t>emp0121@example.com</t>
+  </si>
+  <si>
+    <t>03-1120-5120</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0121</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0121</t>
+  </si>
+  <si>
+    <t>E0122</t>
+  </si>
+  <si>
+    <t>emp0122@example.com</t>
+  </si>
+  <si>
+    <t>03-1121-5121</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0122</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0122</t>
+  </si>
+  <si>
+    <t>E0123</t>
+  </si>
+  <si>
+    <t>emp0123@example.com</t>
+  </si>
+  <si>
+    <t>03-1122-5122</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0123</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0123</t>
+  </si>
+  <si>
+    <t>E0124</t>
+  </si>
+  <si>
+    <t>emp0124@example.com</t>
+  </si>
+  <si>
+    <t>03-1123-5123</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0124</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0124</t>
+  </si>
+  <si>
+    <t>E0125</t>
+  </si>
+  <si>
+    <t>emp0125@example.com</t>
+  </si>
+  <si>
+    <t>03-1124-5124</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0125</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0125</t>
+  </si>
+  <si>
+    <t>E0126</t>
+  </si>
+  <si>
+    <t>emp0126@example.com</t>
+  </si>
+  <si>
+    <t>03-1125-5125</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0126</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0126</t>
+  </si>
+  <si>
+    <t>E0127</t>
+  </si>
+  <si>
+    <t>emp0127@example.com</t>
+  </si>
+  <si>
+    <t>03-1126-5126</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0127</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0127</t>
+  </si>
+  <si>
+    <t>E0128</t>
+  </si>
+  <si>
+    <t>emp0128@example.com</t>
+  </si>
+  <si>
+    <t>03-1127-5127</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0128</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0128</t>
+  </si>
+  <si>
+    <t>E0129</t>
+  </si>
+  <si>
+    <t>emp0129@example.com</t>
+  </si>
+  <si>
+    <t>03-1128-5128</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0129</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0129</t>
+  </si>
+  <si>
+    <t>E0130</t>
+  </si>
+  <si>
+    <t>emp0130@example.com</t>
+  </si>
+  <si>
+    <t>03-1129-5129</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0130</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0130</t>
+  </si>
+  <si>
+    <t>E0131</t>
+  </si>
+  <si>
+    <t>emp0131@example.com</t>
+  </si>
+  <si>
+    <t>03-1130-5130</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0131</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0131</t>
+  </si>
+  <si>
+    <t>E0132</t>
+  </si>
+  <si>
+    <t>emp0132@example.com</t>
+  </si>
+  <si>
+    <t>03-1131-5131</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0132</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0132</t>
+  </si>
+  <si>
+    <t>E0133</t>
+  </si>
+  <si>
+    <t>emp0133@example.com</t>
+  </si>
+  <si>
+    <t>03-1132-5132</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0133</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0133</t>
+  </si>
+  <si>
+    <t>E0134</t>
+  </si>
+  <si>
+    <t>emp0134@example.com</t>
+  </si>
+  <si>
+    <t>03-1133-5133</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0134</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0134</t>
+  </si>
+  <si>
+    <t>E0135</t>
+  </si>
+  <si>
+    <t>emp0135@example.com</t>
+  </si>
+  <si>
+    <t>03-1134-5134</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0135</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0135</t>
+  </si>
+  <si>
+    <t>E0136</t>
+  </si>
+  <si>
+    <t>emp0136@example.com</t>
+  </si>
+  <si>
+    <t>03-1135-5135</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0136</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0136</t>
+  </si>
+  <si>
+    <t>E0137</t>
+  </si>
+  <si>
+    <t>emp0137@example.com</t>
+  </si>
+  <si>
+    <t>03-1136-5136</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0137</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0137</t>
+  </si>
+  <si>
+    <t>E0138</t>
+  </si>
+  <si>
+    <t>emp0138@example.com</t>
+  </si>
+  <si>
+    <t>03-1137-5137</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0138</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0138</t>
+  </si>
+  <si>
+    <t>E0139</t>
+  </si>
+  <si>
+    <t>emp0139@example.com</t>
+  </si>
+  <si>
+    <t>03-1138-5138</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0139</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0139</t>
+  </si>
+  <si>
+    <t>E0140</t>
+  </si>
+  <si>
+    <t>emp0140@example.com</t>
+  </si>
+  <si>
+    <t>03-1139-5139</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0140</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0140</t>
+  </si>
+  <si>
+    <t>E0141</t>
+  </si>
+  <si>
+    <t>emp0141@example.com</t>
+  </si>
+  <si>
+    <t>03-1140-5140</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0141</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0141</t>
+  </si>
+  <si>
+    <t>E0142</t>
+  </si>
+  <si>
+    <t>emp0142@example.com</t>
+  </si>
+  <si>
+    <t>03-1141-5141</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0142</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0142</t>
+  </si>
+  <si>
+    <t>E0143</t>
+  </si>
+  <si>
+    <t>emp0143@example.com</t>
+  </si>
+  <si>
+    <t>03-1142-5142</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0143</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0143</t>
+  </si>
+  <si>
+    <t>E0144</t>
+  </si>
+  <si>
+    <t>emp0144@example.com</t>
+  </si>
+  <si>
+    <t>03-1143-5143</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0144</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0144</t>
+  </si>
+  <si>
+    <t>E0145</t>
+  </si>
+  <si>
+    <t>emp0145@example.com</t>
+  </si>
+  <si>
+    <t>03-1144-5144</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0145</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0145</t>
+  </si>
+  <si>
+    <t>E0146</t>
+  </si>
+  <si>
+    <t>emp0146@example.com</t>
+  </si>
+  <si>
+    <t>03-1145-5145</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0146</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0146</t>
+  </si>
+  <si>
+    <t>E0147</t>
+  </si>
+  <si>
+    <t>emp0147@example.com</t>
+  </si>
+  <si>
+    <t>03-1146-5146</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0147</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0147</t>
+  </si>
+  <si>
+    <t>E0148</t>
+  </si>
+  <si>
+    <t>emp0148@example.com</t>
+  </si>
+  <si>
+    <t>03-1147-5147</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0148</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0148</t>
+  </si>
+  <si>
+    <t>E0149</t>
+  </si>
+  <si>
+    <t>emp0149@example.com</t>
+  </si>
+  <si>
+    <t>03-1148-5148</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0149</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0149</t>
+  </si>
+  <si>
+    <t>E0150</t>
+  </si>
+  <si>
+    <t>emp0150@example.com</t>
+  </si>
+  <si>
+    <t>03-1149-5149</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0150</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0150</t>
+  </si>
+  <si>
+    <t>E0151</t>
+  </si>
+  <si>
+    <t>emp0151@example.com</t>
+  </si>
+  <si>
+    <t>03-1150-5150</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0151</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0151</t>
+  </si>
+  <si>
+    <t>E0152</t>
+  </si>
+  <si>
+    <t>emp0152@example.com</t>
+  </si>
+  <si>
+    <t>03-1151-5151</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0152</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0152</t>
+  </si>
+  <si>
+    <t>E0153</t>
+  </si>
+  <si>
+    <t>emp0153@example.com</t>
+  </si>
+  <si>
+    <t>03-1152-5152</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0153</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0153</t>
+  </si>
+  <si>
+    <t>E0154</t>
+  </si>
+  <si>
+    <t>emp0154@example.com</t>
+  </si>
+  <si>
+    <t>03-1153-5153</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0154</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0154</t>
+  </si>
+  <si>
+    <t>E0155</t>
+  </si>
+  <si>
+    <t>emp0155@example.com</t>
+  </si>
+  <si>
+    <t>03-1154-5154</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0155</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0155</t>
+  </si>
+  <si>
+    <t>E0156</t>
+  </si>
+  <si>
+    <t>emp0156@example.com</t>
+  </si>
+  <si>
+    <t>03-1155-5155</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0156</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0156</t>
+  </si>
+  <si>
+    <t>E0157</t>
+  </si>
+  <si>
+    <t>emp0157@example.com</t>
+  </si>
+  <si>
+    <t>03-1156-5156</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0157</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0157</t>
+  </si>
+  <si>
+    <t>E0158</t>
+  </si>
+  <si>
+    <t>emp0158@example.com</t>
+  </si>
+  <si>
+    <t>03-1157-5157</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0158</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0158</t>
+  </si>
+  <si>
+    <t>E0159</t>
+  </si>
+  <si>
+    <t>emp0159@example.com</t>
+  </si>
+  <si>
+    <t>03-1158-5158</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0159</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0159</t>
+  </si>
+  <si>
+    <t>E0160</t>
+  </si>
+  <si>
+    <t>emp0160@example.com</t>
+  </si>
+  <si>
+    <t>03-1159-5159</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0160</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0160</t>
+  </si>
+  <si>
+    <t>E0161</t>
+  </si>
+  <si>
+    <t>emp0161@example.com</t>
+  </si>
+  <si>
+    <t>03-1160-5160</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0161</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0161</t>
+  </si>
+  <si>
+    <t>E0162</t>
+  </si>
+  <si>
+    <t>emp0162@example.com</t>
+  </si>
+  <si>
+    <t>03-1161-5161</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0162</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0162</t>
+  </si>
+  <si>
+    <t>E0163</t>
+  </si>
+  <si>
+    <t>emp0163@example.com</t>
+  </si>
+  <si>
+    <t>03-1162-5162</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0163</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0163</t>
+  </si>
+  <si>
+    <t>E0164</t>
+  </si>
+  <si>
+    <t>emp0164@example.com</t>
+  </si>
+  <si>
+    <t>03-1163-5163</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0164</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0164</t>
+  </si>
+  <si>
+    <t>E0165</t>
+  </si>
+  <si>
+    <t>emp0165@example.com</t>
+  </si>
+  <si>
+    <t>03-1164-5164</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0165</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0165</t>
+  </si>
+  <si>
+    <t>E0166</t>
+  </si>
+  <si>
+    <t>emp0166@example.com</t>
+  </si>
+  <si>
+    <t>03-1165-5165</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0166</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0166</t>
+  </si>
+  <si>
+    <t>E0167</t>
+  </si>
+  <si>
+    <t>emp0167@example.com</t>
+  </si>
+  <si>
+    <t>03-1166-5166</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0167</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0167</t>
+  </si>
+  <si>
+    <t>E0168</t>
+  </si>
+  <si>
+    <t>emp0168@example.com</t>
+  </si>
+  <si>
+    <t>03-1167-5167</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0168</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0168</t>
+  </si>
+  <si>
+    <t>E0169</t>
+  </si>
+  <si>
+    <t>emp0169@example.com</t>
+  </si>
+  <si>
+    <t>03-1168-5168</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0169</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0169</t>
+  </si>
+  <si>
+    <t>E0170</t>
+  </si>
+  <si>
+    <t>emp0170@example.com</t>
+  </si>
+  <si>
+    <t>03-1169-5169</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0170</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0170</t>
+  </si>
+  <si>
+    <t>E0171</t>
+  </si>
+  <si>
+    <t>emp0171@example.com</t>
+  </si>
+  <si>
+    <t>03-1170-5170</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0171</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0171</t>
+  </si>
+  <si>
+    <t>E0172</t>
+  </si>
+  <si>
+    <t>emp0172@example.com</t>
+  </si>
+  <si>
+    <t>03-1171-5171</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0172</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0172</t>
+  </si>
+  <si>
+    <t>E0173</t>
+  </si>
+  <si>
+    <t>emp0173@example.com</t>
+  </si>
+  <si>
+    <t>03-1172-5172</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0173</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0173</t>
+  </si>
+  <si>
+    <t>E0174</t>
+  </si>
+  <si>
+    <t>emp0174@example.com</t>
+  </si>
+  <si>
+    <t>03-1173-5173</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0174</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0174</t>
+  </si>
+  <si>
+    <t>E0175</t>
+  </si>
+  <si>
+    <t>emp0175@example.com</t>
+  </si>
+  <si>
+    <t>03-1174-5174</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0175</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0175</t>
+  </si>
+  <si>
+    <t>E0176</t>
+  </si>
+  <si>
+    <t>emp0176@example.com</t>
+  </si>
+  <si>
+    <t>03-1175-5175</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0176</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0176</t>
+  </si>
+  <si>
+    <t>E0177</t>
+  </si>
+  <si>
+    <t>emp0177@example.com</t>
+  </si>
+  <si>
+    <t>03-1176-5176</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0177</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0177</t>
+  </si>
+  <si>
+    <t>E0178</t>
+  </si>
+  <si>
+    <t>emp0178@example.com</t>
+  </si>
+  <si>
+    <t>03-1177-5177</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0178</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0178</t>
+  </si>
+  <si>
+    <t>E0179</t>
+  </si>
+  <si>
+    <t>emp0179@example.com</t>
+  </si>
+  <si>
+    <t>03-1178-5178</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0179</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0179</t>
+  </si>
+  <si>
+    <t>E0180</t>
+  </si>
+  <si>
+    <t>emp0180@example.com</t>
+  </si>
+  <si>
+    <t>03-1179-5179</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0180</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0180</t>
+  </si>
+  <si>
+    <t>E0181</t>
+  </si>
+  <si>
+    <t>emp0181@example.com</t>
+  </si>
+  <si>
+    <t>03-1180-5180</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0181</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0181</t>
+  </si>
+  <si>
+    <t>E0182</t>
+  </si>
+  <si>
+    <t>emp0182@example.com</t>
+  </si>
+  <si>
+    <t>03-1181-5181</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0182</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0182</t>
+  </si>
+  <si>
+    <t>E0183</t>
+  </si>
+  <si>
+    <t>emp0183@example.com</t>
+  </si>
+  <si>
+    <t>03-1182-5182</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0183</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0183</t>
+  </si>
+  <si>
+    <t>E0184</t>
+  </si>
+  <si>
+    <t>emp0184@example.com</t>
+  </si>
+  <si>
+    <t>03-1183-5183</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0184</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0184</t>
+  </si>
+  <si>
+    <t>E0185</t>
+  </si>
+  <si>
+    <t>emp0185@example.com</t>
+  </si>
+  <si>
+    <t>03-1184-5184</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0185</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0185</t>
+  </si>
+  <si>
+    <t>E0186</t>
+  </si>
+  <si>
+    <t>emp0186@example.com</t>
+  </si>
+  <si>
+    <t>03-1185-5185</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0186</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0186</t>
+  </si>
+  <si>
+    <t>E0187</t>
+  </si>
+  <si>
+    <t>emp0187@example.com</t>
+  </si>
+  <si>
+    <t>03-1186-5186</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0187</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0187</t>
+  </si>
+  <si>
+    <t>E0188</t>
+  </si>
+  <si>
+    <t>emp0188@example.com</t>
+  </si>
+  <si>
+    <t>03-1187-5187</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0188</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0188</t>
+  </si>
+  <si>
+    <t>E0189</t>
+  </si>
+  <si>
+    <t>emp0189@example.com</t>
+  </si>
+  <si>
+    <t>03-1188-5188</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0189</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0189</t>
+  </si>
+  <si>
+    <t>E0190</t>
+  </si>
+  <si>
+    <t>emp0190@example.com</t>
+  </si>
+  <si>
+    <t>03-1189-5189</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0190</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0190</t>
+  </si>
+  <si>
+    <t>E0191</t>
+  </si>
+  <si>
+    <t>emp0191@example.com</t>
+  </si>
+  <si>
+    <t>03-1190-5190</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0191</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0191</t>
+  </si>
+  <si>
+    <t>E0192</t>
+  </si>
+  <si>
+    <t>emp0192@example.com</t>
+  </si>
+  <si>
+    <t>03-1191-5191</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0192</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0192</t>
+  </si>
+  <si>
+    <t>E0193</t>
+  </si>
+  <si>
+    <t>emp0193@example.com</t>
+  </si>
+  <si>
+    <t>03-1192-5192</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0193</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0193</t>
+  </si>
+  <si>
+    <t>E0194</t>
+  </si>
+  <si>
+    <t>emp0194@example.com</t>
+  </si>
+  <si>
+    <t>03-1193-5193</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0194</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0194</t>
+  </si>
+  <si>
+    <t>E0195</t>
+  </si>
+  <si>
+    <t>emp0195@example.com</t>
+  </si>
+  <si>
+    <t>03-1194-5194</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0195</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0195</t>
+  </si>
+  <si>
+    <t>E0196</t>
+  </si>
+  <si>
+    <t>emp0196@example.com</t>
+  </si>
+  <si>
+    <t>03-1195-5195</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0196</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0196</t>
+  </si>
+  <si>
+    <t>E0197</t>
+  </si>
+  <si>
+    <t>emp0197@example.com</t>
+  </si>
+  <si>
+    <t>03-1196-5196</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0197</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0197</t>
+  </si>
+  <si>
+    <t>E0198</t>
+  </si>
+  <si>
+    <t>emp0198@example.com</t>
+  </si>
+  <si>
+    <t>03-1197-5197</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0198</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0198</t>
+  </si>
+  <si>
+    <t>E0199</t>
+  </si>
+  <si>
+    <t>emp0199@example.com</t>
+  </si>
+  <si>
+    <t>03-1198-5198</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0199</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0199</t>
+  </si>
+  <si>
+    <t>E0200</t>
+  </si>
+  <si>
+    <t>emp0200@example.com</t>
+  </si>
+  <si>
+    <t>03-1199-5199</t>
+  </si>
+  <si>
+    <t>C:\Users\ynisi\Documents\employees\E0200</t>
+  </si>
+  <si>
+    <t>https://intranet.example.com/profile/E0200</t>
   </si>
 </sst>
 </file>
@@ -214,8 +3566,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,7 +3886,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE17E89B-2BB2-4248-9A10-7C79396DF866}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1023853-1DF3-4BC7-8BD1-00847C8B2085}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -598,7 +3953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF6ABEA9-760D-446D-A4C1-F14140BFDE91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9089E528-CDB8-4DFB-B02E-08AC2C19BAC4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -653,7 +4008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC3DB7A-E3AC-4EA7-ADC7-5635489D32AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030467EF-5EBE-4F2C-BFAA-E431A7184B9E}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -697,7 +4052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C28695-3954-433D-A984-169399583E58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D25453E-DCDA-4DF9-9F22-8696B0EFD572}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -761,4 +4116,6447 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3765BAD-2113-42D2-863A-BB58581AC3A0}">
+  <dimension ref="A1:J201"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="1">
+        <v>42095</v>
+      </c>
+      <c r="H2">
+        <v>250000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="1">
+        <v>42102</v>
+      </c>
+      <c r="H3">
+        <v>255000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="1">
+        <v>42109</v>
+      </c>
+      <c r="H4">
+        <v>260000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="1">
+        <v>42116</v>
+      </c>
+      <c r="H5">
+        <v>265000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="1">
+        <v>42123</v>
+      </c>
+      <c r="H6">
+        <v>270000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="1">
+        <v>42130</v>
+      </c>
+      <c r="H7">
+        <v>275000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1">
+        <v>42137</v>
+      </c>
+      <c r="H8">
+        <v>280000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="1">
+        <v>42144</v>
+      </c>
+      <c r="H9">
+        <v>285000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="1">
+        <v>42151</v>
+      </c>
+      <c r="H10">
+        <v>290000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>115</v>
+      </c>
+      <c r="J10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="1">
+        <v>42158</v>
+      </c>
+      <c r="H11">
+        <v>295000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="1">
+        <v>42165</v>
+      </c>
+      <c r="H12">
+        <v>300000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="1">
+        <v>42172</v>
+      </c>
+      <c r="H13">
+        <v>305000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="1">
+        <v>42179</v>
+      </c>
+      <c r="H14">
+        <v>310000</v>
+      </c>
+      <c r="I14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="1">
+        <v>42186</v>
+      </c>
+      <c r="H15">
+        <v>315000</v>
+      </c>
+      <c r="I15" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" s="1">
+        <v>42193</v>
+      </c>
+      <c r="H16">
+        <v>320000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G17" s="1">
+        <v>42200</v>
+      </c>
+      <c r="H17">
+        <v>325000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="1">
+        <v>42207</v>
+      </c>
+      <c r="H18">
+        <v>330000</v>
+      </c>
+      <c r="I18" t="s">
+        <v>162</v>
+      </c>
+      <c r="J18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>166</v>
+      </c>
+      <c r="F19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G19" s="1">
+        <v>42214</v>
+      </c>
+      <c r="H19">
+        <v>335000</v>
+      </c>
+      <c r="I19" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="1">
+        <v>42221</v>
+      </c>
+      <c r="H20">
+        <v>340000</v>
+      </c>
+      <c r="I20" t="s">
+        <v>174</v>
+      </c>
+      <c r="J20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21" t="s">
+        <v>179</v>
+      </c>
+      <c r="G21" s="1">
+        <v>42228</v>
+      </c>
+      <c r="H21">
+        <v>345000</v>
+      </c>
+      <c r="I21" t="s">
+        <v>180</v>
+      </c>
+      <c r="J21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F22" t="s">
+        <v>185</v>
+      </c>
+      <c r="G22" s="1">
+        <v>42235</v>
+      </c>
+      <c r="H22">
+        <v>350000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" t="s">
+        <v>191</v>
+      </c>
+      <c r="G23" s="1">
+        <v>42242</v>
+      </c>
+      <c r="H23">
+        <v>355000</v>
+      </c>
+      <c r="I23" t="s">
+        <v>192</v>
+      </c>
+      <c r="J23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" t="s">
+        <v>196</v>
+      </c>
+      <c r="G24" s="1">
+        <v>42249</v>
+      </c>
+      <c r="H24">
+        <v>360000</v>
+      </c>
+      <c r="I24" t="s">
+        <v>197</v>
+      </c>
+      <c r="J24" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>201</v>
+      </c>
+      <c r="F25" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="1">
+        <v>42256</v>
+      </c>
+      <c r="H25">
+        <v>365000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>203</v>
+      </c>
+      <c r="J25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" t="s">
+        <v>208</v>
+      </c>
+      <c r="G26" s="1">
+        <v>42263</v>
+      </c>
+      <c r="H26">
+        <v>370000</v>
+      </c>
+      <c r="I26" t="s">
+        <v>209</v>
+      </c>
+      <c r="J26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" t="s">
+        <v>213</v>
+      </c>
+      <c r="F27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G27" s="1">
+        <v>42270</v>
+      </c>
+      <c r="H27">
+        <v>375000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>215</v>
+      </c>
+      <c r="J27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="1">
+        <v>42277</v>
+      </c>
+      <c r="H28">
+        <v>380000</v>
+      </c>
+      <c r="I28" t="s">
+        <v>221</v>
+      </c>
+      <c r="J28" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" t="s">
+        <v>225</v>
+      </c>
+      <c r="F29" t="s">
+        <v>226</v>
+      </c>
+      <c r="G29" s="1">
+        <v>42284</v>
+      </c>
+      <c r="H29">
+        <v>385000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>227</v>
+      </c>
+      <c r="J29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" t="s">
+        <v>231</v>
+      </c>
+      <c r="F30" t="s">
+        <v>232</v>
+      </c>
+      <c r="G30" s="1">
+        <v>42291</v>
+      </c>
+      <c r="H30">
+        <v>390000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>233</v>
+      </c>
+      <c r="J30" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" t="s">
+        <v>237</v>
+      </c>
+      <c r="F31" t="s">
+        <v>238</v>
+      </c>
+      <c r="G31" s="1">
+        <v>42298</v>
+      </c>
+      <c r="H31">
+        <v>395000</v>
+      </c>
+      <c r="I31" t="s">
+        <v>239</v>
+      </c>
+      <c r="J31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" t="s">
+        <v>243</v>
+      </c>
+      <c r="F32" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="1">
+        <v>42305</v>
+      </c>
+      <c r="H32">
+        <v>400000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>245</v>
+      </c>
+      <c r="J32" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" t="s">
+        <v>250</v>
+      </c>
+      <c r="G33" s="1">
+        <v>42312</v>
+      </c>
+      <c r="H33">
+        <v>405000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>251</v>
+      </c>
+      <c r="J33" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F34" t="s">
+        <v>256</v>
+      </c>
+      <c r="G34" s="1">
+        <v>42319</v>
+      </c>
+      <c r="H34">
+        <v>410000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>257</v>
+      </c>
+      <c r="J34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>259</v>
+      </c>
+      <c r="B35" t="s">
+        <v>260</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" t="s">
+        <v>261</v>
+      </c>
+      <c r="F35" t="s">
+        <v>262</v>
+      </c>
+      <c r="G35" s="1">
+        <v>42326</v>
+      </c>
+      <c r="H35">
+        <v>415000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>263</v>
+      </c>
+      <c r="J35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>265</v>
+      </c>
+      <c r="B36" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" t="s">
+        <v>267</v>
+      </c>
+      <c r="F36" t="s">
+        <v>268</v>
+      </c>
+      <c r="G36" s="1">
+        <v>42333</v>
+      </c>
+      <c r="H36">
+        <v>420000</v>
+      </c>
+      <c r="I36" t="s">
+        <v>269</v>
+      </c>
+      <c r="J36" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>271</v>
+      </c>
+      <c r="B37" t="s">
+        <v>272</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" t="s">
+        <v>273</v>
+      </c>
+      <c r="F37" t="s">
+        <v>274</v>
+      </c>
+      <c r="G37" s="1">
+        <v>42340</v>
+      </c>
+      <c r="H37">
+        <v>425000</v>
+      </c>
+      <c r="I37" t="s">
+        <v>275</v>
+      </c>
+      <c r="J37" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>277</v>
+      </c>
+      <c r="B38" t="s">
+        <v>278</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>279</v>
+      </c>
+      <c r="F38" t="s">
+        <v>280</v>
+      </c>
+      <c r="G38" s="1">
+        <v>42347</v>
+      </c>
+      <c r="H38">
+        <v>430000</v>
+      </c>
+      <c r="I38" t="s">
+        <v>281</v>
+      </c>
+      <c r="J38" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" t="s">
+        <v>285</v>
+      </c>
+      <c r="F39" t="s">
+        <v>286</v>
+      </c>
+      <c r="G39" s="1">
+        <v>42354</v>
+      </c>
+      <c r="H39">
+        <v>435000</v>
+      </c>
+      <c r="I39" t="s">
+        <v>287</v>
+      </c>
+      <c r="J39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" t="s">
+        <v>290</v>
+      </c>
+      <c r="C40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
+      </c>
+      <c r="E40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F40" t="s">
+        <v>292</v>
+      </c>
+      <c r="G40" s="1">
+        <v>42361</v>
+      </c>
+      <c r="H40">
+        <v>440000</v>
+      </c>
+      <c r="I40" t="s">
+        <v>293</v>
+      </c>
+      <c r="J40" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>295</v>
+      </c>
+      <c r="B41" t="s">
+        <v>296</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" t="s">
+        <v>297</v>
+      </c>
+      <c r="F41" t="s">
+        <v>298</v>
+      </c>
+      <c r="G41" s="1">
+        <v>42368</v>
+      </c>
+      <c r="H41">
+        <v>445000</v>
+      </c>
+      <c r="I41" t="s">
+        <v>299</v>
+      </c>
+      <c r="J41" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>301</v>
+      </c>
+      <c r="B42" t="s">
+        <v>302</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" t="s">
+        <v>303</v>
+      </c>
+      <c r="F42" t="s">
+        <v>304</v>
+      </c>
+      <c r="G42" s="1">
+        <v>42375</v>
+      </c>
+      <c r="H42">
+        <v>450000</v>
+      </c>
+      <c r="I42" t="s">
+        <v>305</v>
+      </c>
+      <c r="J42" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>307</v>
+      </c>
+      <c r="B43" t="s">
+        <v>308</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F43" t="s">
+        <v>310</v>
+      </c>
+      <c r="G43" s="1">
+        <v>42382</v>
+      </c>
+      <c r="H43">
+        <v>455000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>311</v>
+      </c>
+      <c r="J43" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>313</v>
+      </c>
+      <c r="B44" t="s">
+        <v>314</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>315</v>
+      </c>
+      <c r="F44" t="s">
+        <v>316</v>
+      </c>
+      <c r="G44" s="1">
+        <v>42389</v>
+      </c>
+      <c r="H44">
+        <v>460000</v>
+      </c>
+      <c r="I44" t="s">
+        <v>317</v>
+      </c>
+      <c r="J44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>319</v>
+      </c>
+      <c r="B45" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" t="s">
+        <v>321</v>
+      </c>
+      <c r="F45" t="s">
+        <v>322</v>
+      </c>
+      <c r="G45" s="1">
+        <v>42396</v>
+      </c>
+      <c r="H45">
+        <v>465000</v>
+      </c>
+      <c r="I45" t="s">
+        <v>323</v>
+      </c>
+      <c r="J45" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>325</v>
+      </c>
+      <c r="B46" t="s">
+        <v>326</v>
+      </c>
+      <c r="C46" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>327</v>
+      </c>
+      <c r="F46" t="s">
+        <v>328</v>
+      </c>
+      <c r="G46" s="1">
+        <v>42403</v>
+      </c>
+      <c r="H46">
+        <v>470000</v>
+      </c>
+      <c r="I46" t="s">
+        <v>329</v>
+      </c>
+      <c r="J46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>331</v>
+      </c>
+      <c r="B47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" t="s">
+        <v>333</v>
+      </c>
+      <c r="F47" t="s">
+        <v>334</v>
+      </c>
+      <c r="G47" s="1">
+        <v>42410</v>
+      </c>
+      <c r="H47">
+        <v>475000</v>
+      </c>
+      <c r="I47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J47" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>337</v>
+      </c>
+      <c r="B48" t="s">
+        <v>338</v>
+      </c>
+      <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" t="s">
+        <v>339</v>
+      </c>
+      <c r="F48" t="s">
+        <v>340</v>
+      </c>
+      <c r="G48" s="1">
+        <v>42417</v>
+      </c>
+      <c r="H48">
+        <v>480000</v>
+      </c>
+      <c r="I48" t="s">
+        <v>341</v>
+      </c>
+      <c r="J48" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>343</v>
+      </c>
+      <c r="B49" t="s">
+        <v>344</v>
+      </c>
+      <c r="C49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>345</v>
+      </c>
+      <c r="F49" t="s">
+        <v>346</v>
+      </c>
+      <c r="G49" s="1">
+        <v>42424</v>
+      </c>
+      <c r="H49">
+        <v>485000</v>
+      </c>
+      <c r="I49" t="s">
+        <v>347</v>
+      </c>
+      <c r="J49" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>349</v>
+      </c>
+      <c r="B50" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" t="s">
+        <v>351</v>
+      </c>
+      <c r="F50" t="s">
+        <v>352</v>
+      </c>
+      <c r="G50" s="1">
+        <v>42431</v>
+      </c>
+      <c r="H50">
+        <v>490000</v>
+      </c>
+      <c r="I50" t="s">
+        <v>353</v>
+      </c>
+      <c r="J50" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>355</v>
+      </c>
+      <c r="B51" t="s">
+        <v>356</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" t="s">
+        <v>357</v>
+      </c>
+      <c r="F51" t="s">
+        <v>358</v>
+      </c>
+      <c r="G51" s="1">
+        <v>42438</v>
+      </c>
+      <c r="H51">
+        <v>495000</v>
+      </c>
+      <c r="I51" t="s">
+        <v>359</v>
+      </c>
+      <c r="J51" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>361</v>
+      </c>
+      <c r="B52" t="s">
+        <v>362</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" t="s">
+        <v>363</v>
+      </c>
+      <c r="F52" t="s">
+        <v>364</v>
+      </c>
+      <c r="G52" s="1">
+        <v>42445</v>
+      </c>
+      <c r="H52">
+        <v>500000</v>
+      </c>
+      <c r="I52" t="s">
+        <v>365</v>
+      </c>
+      <c r="J52" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>367</v>
+      </c>
+      <c r="B53" t="s">
+        <v>368</v>
+      </c>
+      <c r="C53" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" t="s">
+        <v>369</v>
+      </c>
+      <c r="F53" t="s">
+        <v>370</v>
+      </c>
+      <c r="G53" s="1">
+        <v>42452</v>
+      </c>
+      <c r="H53">
+        <v>505000</v>
+      </c>
+      <c r="I53" t="s">
+        <v>371</v>
+      </c>
+      <c r="J53" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>373</v>
+      </c>
+      <c r="B54" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" t="s">
+        <v>375</v>
+      </c>
+      <c r="F54" t="s">
+        <v>376</v>
+      </c>
+      <c r="G54" s="1">
+        <v>42459</v>
+      </c>
+      <c r="H54">
+        <v>510000</v>
+      </c>
+      <c r="I54" t="s">
+        <v>377</v>
+      </c>
+      <c r="J54" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>379</v>
+      </c>
+      <c r="B55" t="s">
+        <v>380</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" t="s">
+        <v>381</v>
+      </c>
+      <c r="F55" t="s">
+        <v>382</v>
+      </c>
+      <c r="G55" s="1">
+        <v>42466</v>
+      </c>
+      <c r="H55">
+        <v>515000</v>
+      </c>
+      <c r="I55" t="s">
+        <v>383</v>
+      </c>
+      <c r="J55" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>385</v>
+      </c>
+      <c r="B56" t="s">
+        <v>386</v>
+      </c>
+      <c r="C56" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>387</v>
+      </c>
+      <c r="F56" t="s">
+        <v>388</v>
+      </c>
+      <c r="G56" s="1">
+        <v>42473</v>
+      </c>
+      <c r="H56">
+        <v>520000</v>
+      </c>
+      <c r="I56" t="s">
+        <v>389</v>
+      </c>
+      <c r="J56" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>391</v>
+      </c>
+      <c r="B57" t="s">
+        <v>392</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" t="s">
+        <v>393</v>
+      </c>
+      <c r="F57" t="s">
+        <v>394</v>
+      </c>
+      <c r="G57" s="1">
+        <v>42480</v>
+      </c>
+      <c r="H57">
+        <v>525000</v>
+      </c>
+      <c r="I57" t="s">
+        <v>395</v>
+      </c>
+      <c r="J57" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>397</v>
+      </c>
+      <c r="B58" t="s">
+        <v>398</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" t="s">
+        <v>399</v>
+      </c>
+      <c r="F58" t="s">
+        <v>400</v>
+      </c>
+      <c r="G58" s="1">
+        <v>42487</v>
+      </c>
+      <c r="H58">
+        <v>530000</v>
+      </c>
+      <c r="I58" t="s">
+        <v>401</v>
+      </c>
+      <c r="J58" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>403</v>
+      </c>
+      <c r="B59" t="s">
+        <v>404</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" t="s">
+        <v>405</v>
+      </c>
+      <c r="F59" t="s">
+        <v>406</v>
+      </c>
+      <c r="G59" s="1">
+        <v>42494</v>
+      </c>
+      <c r="H59">
+        <v>535000</v>
+      </c>
+      <c r="I59" t="s">
+        <v>407</v>
+      </c>
+      <c r="J59" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>409</v>
+      </c>
+      <c r="B60" t="s">
+        <v>410</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" t="s">
+        <v>411</v>
+      </c>
+      <c r="F60" t="s">
+        <v>412</v>
+      </c>
+      <c r="G60" s="1">
+        <v>42501</v>
+      </c>
+      <c r="H60">
+        <v>540000</v>
+      </c>
+      <c r="I60" t="s">
+        <v>413</v>
+      </c>
+      <c r="J60" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>415</v>
+      </c>
+      <c r="B61" t="s">
+        <v>416</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" t="s">
+        <v>417</v>
+      </c>
+      <c r="F61" t="s">
+        <v>418</v>
+      </c>
+      <c r="G61" s="1">
+        <v>42508</v>
+      </c>
+      <c r="H61">
+        <v>545000</v>
+      </c>
+      <c r="I61" t="s">
+        <v>419</v>
+      </c>
+      <c r="J61" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>421</v>
+      </c>
+      <c r="B62" t="s">
+        <v>422</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62" t="s">
+        <v>423</v>
+      </c>
+      <c r="F62" t="s">
+        <v>424</v>
+      </c>
+      <c r="G62" s="1">
+        <v>42515</v>
+      </c>
+      <c r="H62">
+        <v>550000</v>
+      </c>
+      <c r="I62" t="s">
+        <v>425</v>
+      </c>
+      <c r="J62" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>427</v>
+      </c>
+      <c r="B63" t="s">
+        <v>428</v>
+      </c>
+      <c r="C63" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" t="s">
+        <v>62</v>
+      </c>
+      <c r="E63" t="s">
+        <v>429</v>
+      </c>
+      <c r="F63" t="s">
+        <v>430</v>
+      </c>
+      <c r="G63" s="1">
+        <v>42522</v>
+      </c>
+      <c r="H63">
+        <v>555000</v>
+      </c>
+      <c r="I63" t="s">
+        <v>431</v>
+      </c>
+      <c r="J63" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>433</v>
+      </c>
+      <c r="B64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C64" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" t="s">
+        <v>435</v>
+      </c>
+      <c r="F64" t="s">
+        <v>436</v>
+      </c>
+      <c r="G64" s="1">
+        <v>42529</v>
+      </c>
+      <c r="H64">
+        <v>560000</v>
+      </c>
+      <c r="I64" t="s">
+        <v>437</v>
+      </c>
+      <c r="J64" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>439</v>
+      </c>
+      <c r="B65" t="s">
+        <v>440</v>
+      </c>
+      <c r="C65" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" t="s">
+        <v>441</v>
+      </c>
+      <c r="F65" t="s">
+        <v>442</v>
+      </c>
+      <c r="G65" s="1">
+        <v>42536</v>
+      </c>
+      <c r="H65">
+        <v>565000</v>
+      </c>
+      <c r="I65" t="s">
+        <v>443</v>
+      </c>
+      <c r="J65" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" t="s">
+        <v>446</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" t="s">
+        <v>447</v>
+      </c>
+      <c r="F66" t="s">
+        <v>448</v>
+      </c>
+      <c r="G66" s="1">
+        <v>42543</v>
+      </c>
+      <c r="H66">
+        <v>570000</v>
+      </c>
+      <c r="I66" t="s">
+        <v>449</v>
+      </c>
+      <c r="J66" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>451</v>
+      </c>
+      <c r="B67" t="s">
+        <v>452</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" t="s">
+        <v>453</v>
+      </c>
+      <c r="F67" t="s">
+        <v>454</v>
+      </c>
+      <c r="G67" s="1">
+        <v>42550</v>
+      </c>
+      <c r="H67">
+        <v>575000</v>
+      </c>
+      <c r="I67" t="s">
+        <v>455</v>
+      </c>
+      <c r="J67" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>457</v>
+      </c>
+      <c r="B68" t="s">
+        <v>458</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" t="s">
+        <v>459</v>
+      </c>
+      <c r="F68" t="s">
+        <v>460</v>
+      </c>
+      <c r="G68" s="1">
+        <v>42557</v>
+      </c>
+      <c r="H68">
+        <v>580000</v>
+      </c>
+      <c r="I68" t="s">
+        <v>461</v>
+      </c>
+      <c r="J68" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>463</v>
+      </c>
+      <c r="B69" t="s">
+        <v>464</v>
+      </c>
+      <c r="C69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" t="s">
+        <v>465</v>
+      </c>
+      <c r="F69" t="s">
+        <v>466</v>
+      </c>
+      <c r="G69" s="1">
+        <v>42564</v>
+      </c>
+      <c r="H69">
+        <v>585000</v>
+      </c>
+      <c r="I69" t="s">
+        <v>467</v>
+      </c>
+      <c r="J69" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>469</v>
+      </c>
+      <c r="B70" t="s">
+        <v>470</v>
+      </c>
+      <c r="C70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" t="s">
+        <v>471</v>
+      </c>
+      <c r="F70" t="s">
+        <v>472</v>
+      </c>
+      <c r="G70" s="1">
+        <v>42571</v>
+      </c>
+      <c r="H70">
+        <v>590000</v>
+      </c>
+      <c r="I70" t="s">
+        <v>473</v>
+      </c>
+      <c r="J70" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>475</v>
+      </c>
+      <c r="B71" t="s">
+        <v>476</v>
+      </c>
+      <c r="C71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>477</v>
+      </c>
+      <c r="F71" t="s">
+        <v>478</v>
+      </c>
+      <c r="G71" s="1">
+        <v>42578</v>
+      </c>
+      <c r="H71">
+        <v>595000</v>
+      </c>
+      <c r="I71" t="s">
+        <v>479</v>
+      </c>
+      <c r="J71" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>481</v>
+      </c>
+      <c r="B72" t="s">
+        <v>482</v>
+      </c>
+      <c r="C72" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" t="s">
+        <v>483</v>
+      </c>
+      <c r="F72" t="s">
+        <v>484</v>
+      </c>
+      <c r="G72" s="1">
+        <v>42585</v>
+      </c>
+      <c r="H72">
+        <v>600000</v>
+      </c>
+      <c r="I72" t="s">
+        <v>485</v>
+      </c>
+      <c r="J72" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>487</v>
+      </c>
+      <c r="B73" t="s">
+        <v>488</v>
+      </c>
+      <c r="C73" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" t="s">
+        <v>489</v>
+      </c>
+      <c r="F73" t="s">
+        <v>490</v>
+      </c>
+      <c r="G73" s="1">
+        <v>42592</v>
+      </c>
+      <c r="H73">
+        <v>605000</v>
+      </c>
+      <c r="I73" t="s">
+        <v>491</v>
+      </c>
+      <c r="J73" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>493</v>
+      </c>
+      <c r="B74" t="s">
+        <v>494</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" t="s">
+        <v>495</v>
+      </c>
+      <c r="F74" t="s">
+        <v>496</v>
+      </c>
+      <c r="G74" s="1">
+        <v>42599</v>
+      </c>
+      <c r="H74">
+        <v>610000</v>
+      </c>
+      <c r="I74" t="s">
+        <v>497</v>
+      </c>
+      <c r="J74" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>499</v>
+      </c>
+      <c r="B75" t="s">
+        <v>500</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" t="s">
+        <v>501</v>
+      </c>
+      <c r="F75" t="s">
+        <v>502</v>
+      </c>
+      <c r="G75" s="1">
+        <v>42606</v>
+      </c>
+      <c r="H75">
+        <v>615000</v>
+      </c>
+      <c r="I75" t="s">
+        <v>503</v>
+      </c>
+      <c r="J75" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>505</v>
+      </c>
+      <c r="B76" t="s">
+        <v>506</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" t="s">
+        <v>507</v>
+      </c>
+      <c r="F76" t="s">
+        <v>508</v>
+      </c>
+      <c r="G76" s="1">
+        <v>42613</v>
+      </c>
+      <c r="H76">
+        <v>620000</v>
+      </c>
+      <c r="I76" t="s">
+        <v>509</v>
+      </c>
+      <c r="J76" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>511</v>
+      </c>
+      <c r="B77" t="s">
+        <v>512</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>55</v>
+      </c>
+      <c r="E77" t="s">
+        <v>513</v>
+      </c>
+      <c r="F77" t="s">
+        <v>514</v>
+      </c>
+      <c r="G77" s="1">
+        <v>42620</v>
+      </c>
+      <c r="H77">
+        <v>625000</v>
+      </c>
+      <c r="I77" t="s">
+        <v>515</v>
+      </c>
+      <c r="J77" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>517</v>
+      </c>
+      <c r="B78" t="s">
+        <v>518</v>
+      </c>
+      <c r="C78" t="s">
+        <v>84</v>
+      </c>
+      <c r="D78" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" t="s">
+        <v>519</v>
+      </c>
+      <c r="F78" t="s">
+        <v>520</v>
+      </c>
+      <c r="G78" s="1">
+        <v>42627</v>
+      </c>
+      <c r="H78">
+        <v>630000</v>
+      </c>
+      <c r="I78" t="s">
+        <v>521</v>
+      </c>
+      <c r="J78" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>523</v>
+      </c>
+      <c r="B79" t="s">
+        <v>524</v>
+      </c>
+      <c r="C79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" t="s">
+        <v>525</v>
+      </c>
+      <c r="F79" t="s">
+        <v>526</v>
+      </c>
+      <c r="G79" s="1">
+        <v>42634</v>
+      </c>
+      <c r="H79">
+        <v>635000</v>
+      </c>
+      <c r="I79" t="s">
+        <v>527</v>
+      </c>
+      <c r="J79" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>529</v>
+      </c>
+      <c r="B80" t="s">
+        <v>530</v>
+      </c>
+      <c r="C80" t="s">
+        <v>99</v>
+      </c>
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" t="s">
+        <v>531</v>
+      </c>
+      <c r="F80" t="s">
+        <v>532</v>
+      </c>
+      <c r="G80" s="1">
+        <v>42641</v>
+      </c>
+      <c r="H80">
+        <v>640000</v>
+      </c>
+      <c r="I80" t="s">
+        <v>533</v>
+      </c>
+      <c r="J80" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>535</v>
+      </c>
+      <c r="B81" t="s">
+        <v>536</v>
+      </c>
+      <c r="C81" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" t="s">
+        <v>85</v>
+      </c>
+      <c r="E81" t="s">
+        <v>537</v>
+      </c>
+      <c r="F81" t="s">
+        <v>538</v>
+      </c>
+      <c r="G81" s="1">
+        <v>42648</v>
+      </c>
+      <c r="H81">
+        <v>645000</v>
+      </c>
+      <c r="I81" t="s">
+        <v>539</v>
+      </c>
+      <c r="J81" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>541</v>
+      </c>
+      <c r="B82" t="s">
+        <v>542</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>55</v>
+      </c>
+      <c r="E82" t="s">
+        <v>543</v>
+      </c>
+      <c r="F82" t="s">
+        <v>544</v>
+      </c>
+      <c r="G82" s="1">
+        <v>42655</v>
+      </c>
+      <c r="H82">
+        <v>650000</v>
+      </c>
+      <c r="I82" t="s">
+        <v>545</v>
+      </c>
+      <c r="J82" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>547</v>
+      </c>
+      <c r="B83" t="s">
+        <v>548</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" t="s">
+        <v>62</v>
+      </c>
+      <c r="E83" t="s">
+        <v>549</v>
+      </c>
+      <c r="F83" t="s">
+        <v>550</v>
+      </c>
+      <c r="G83" s="1">
+        <v>42662</v>
+      </c>
+      <c r="H83">
+        <v>655000</v>
+      </c>
+      <c r="I83" t="s">
+        <v>551</v>
+      </c>
+      <c r="J83" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>553</v>
+      </c>
+      <c r="B84" t="s">
+        <v>554</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" t="s">
+        <v>555</v>
+      </c>
+      <c r="F84" t="s">
+        <v>556</v>
+      </c>
+      <c r="G84" s="1">
+        <v>42669</v>
+      </c>
+      <c r="H84">
+        <v>660000</v>
+      </c>
+      <c r="I84" t="s">
+        <v>557</v>
+      </c>
+      <c r="J84" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>559</v>
+      </c>
+      <c r="B85" t="s">
+        <v>560</v>
+      </c>
+      <c r="C85" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" t="s">
+        <v>561</v>
+      </c>
+      <c r="F85" t="s">
+        <v>562</v>
+      </c>
+      <c r="G85" s="1">
+        <v>42676</v>
+      </c>
+      <c r="H85">
+        <v>665000</v>
+      </c>
+      <c r="I85" t="s">
+        <v>563</v>
+      </c>
+      <c r="J85" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>565</v>
+      </c>
+      <c r="B86" t="s">
+        <v>566</v>
+      </c>
+      <c r="C86" t="s">
+        <v>84</v>
+      </c>
+      <c r="D86" t="s">
+        <v>85</v>
+      </c>
+      <c r="E86" t="s">
+        <v>567</v>
+      </c>
+      <c r="F86" t="s">
+        <v>568</v>
+      </c>
+      <c r="G86" s="1">
+        <v>42683</v>
+      </c>
+      <c r="H86">
+        <v>670000</v>
+      </c>
+      <c r="I86" t="s">
+        <v>569</v>
+      </c>
+      <c r="J86" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>571</v>
+      </c>
+      <c r="B87" t="s">
+        <v>572</v>
+      </c>
+      <c r="C87" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" t="s">
+        <v>55</v>
+      </c>
+      <c r="E87" t="s">
+        <v>573</v>
+      </c>
+      <c r="F87" t="s">
+        <v>574</v>
+      </c>
+      <c r="G87" s="1">
+        <v>42690</v>
+      </c>
+      <c r="H87">
+        <v>675000</v>
+      </c>
+      <c r="I87" t="s">
+        <v>575</v>
+      </c>
+      <c r="J87" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>577</v>
+      </c>
+      <c r="B88" t="s">
+        <v>578</v>
+      </c>
+      <c r="C88" t="s">
+        <v>99</v>
+      </c>
+      <c r="D88" t="s">
+        <v>62</v>
+      </c>
+      <c r="E88" t="s">
+        <v>579</v>
+      </c>
+      <c r="F88" t="s">
+        <v>580</v>
+      </c>
+      <c r="G88" s="1">
+        <v>42697</v>
+      </c>
+      <c r="H88">
+        <v>680000</v>
+      </c>
+      <c r="I88" t="s">
+        <v>581</v>
+      </c>
+      <c r="J88" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>583</v>
+      </c>
+      <c r="B89" t="s">
+        <v>584</v>
+      </c>
+      <c r="C89" t="s">
+        <v>106</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" t="s">
+        <v>585</v>
+      </c>
+      <c r="F89" t="s">
+        <v>586</v>
+      </c>
+      <c r="G89" s="1">
+        <v>42704</v>
+      </c>
+      <c r="H89">
+        <v>685000</v>
+      </c>
+      <c r="I89" t="s">
+        <v>587</v>
+      </c>
+      <c r="J89" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>589</v>
+      </c>
+      <c r="B90" t="s">
+        <v>590</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" t="s">
+        <v>591</v>
+      </c>
+      <c r="F90" t="s">
+        <v>592</v>
+      </c>
+      <c r="G90" s="1">
+        <v>42711</v>
+      </c>
+      <c r="H90">
+        <v>690000</v>
+      </c>
+      <c r="I90" t="s">
+        <v>593</v>
+      </c>
+      <c r="J90" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>595</v>
+      </c>
+      <c r="B91" t="s">
+        <v>596</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
+        <v>85</v>
+      </c>
+      <c r="E91" t="s">
+        <v>597</v>
+      </c>
+      <c r="F91" t="s">
+        <v>598</v>
+      </c>
+      <c r="G91" s="1">
+        <v>42718</v>
+      </c>
+      <c r="H91">
+        <v>695000</v>
+      </c>
+      <c r="I91" t="s">
+        <v>599</v>
+      </c>
+      <c r="J91" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>601</v>
+      </c>
+      <c r="B92" t="s">
+        <v>602</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>55</v>
+      </c>
+      <c r="E92" t="s">
+        <v>603</v>
+      </c>
+      <c r="F92" t="s">
+        <v>604</v>
+      </c>
+      <c r="G92" s="1">
+        <v>42725</v>
+      </c>
+      <c r="H92">
+        <v>700000</v>
+      </c>
+      <c r="I92" t="s">
+        <v>605</v>
+      </c>
+      <c r="J92" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>607</v>
+      </c>
+      <c r="B93" t="s">
+        <v>608</v>
+      </c>
+      <c r="C93" t="s">
+        <v>76</v>
+      </c>
+      <c r="D93" t="s">
+        <v>62</v>
+      </c>
+      <c r="E93" t="s">
+        <v>609</v>
+      </c>
+      <c r="F93" t="s">
+        <v>610</v>
+      </c>
+      <c r="G93" s="1">
+        <v>42732</v>
+      </c>
+      <c r="H93">
+        <v>705000</v>
+      </c>
+      <c r="I93" t="s">
+        <v>611</v>
+      </c>
+      <c r="J93" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>613</v>
+      </c>
+      <c r="B94" t="s">
+        <v>614</v>
+      </c>
+      <c r="C94" t="s">
+        <v>84</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" t="s">
+        <v>615</v>
+      </c>
+      <c r="F94" t="s">
+        <v>616</v>
+      </c>
+      <c r="G94" s="1">
+        <v>42739</v>
+      </c>
+      <c r="H94">
+        <v>710000</v>
+      </c>
+      <c r="I94" t="s">
+        <v>617</v>
+      </c>
+      <c r="J94" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>619</v>
+      </c>
+      <c r="B95" t="s">
+        <v>620</v>
+      </c>
+      <c r="C95" t="s">
+        <v>92</v>
+      </c>
+      <c r="D95" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" t="s">
+        <v>621</v>
+      </c>
+      <c r="F95" t="s">
+        <v>622</v>
+      </c>
+      <c r="G95" s="1">
+        <v>42746</v>
+      </c>
+      <c r="H95">
+        <v>715000</v>
+      </c>
+      <c r="I95" t="s">
+        <v>623</v>
+      </c>
+      <c r="J95" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>625</v>
+      </c>
+      <c r="B96" t="s">
+        <v>626</v>
+      </c>
+      <c r="C96" t="s">
+        <v>99</v>
+      </c>
+      <c r="D96" t="s">
+        <v>85</v>
+      </c>
+      <c r="E96" t="s">
+        <v>627</v>
+      </c>
+      <c r="F96" t="s">
+        <v>628</v>
+      </c>
+      <c r="G96" s="1">
+        <v>42753</v>
+      </c>
+      <c r="H96">
+        <v>720000</v>
+      </c>
+      <c r="I96" t="s">
+        <v>629</v>
+      </c>
+      <c r="J96" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>631</v>
+      </c>
+      <c r="B97" t="s">
+        <v>632</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>55</v>
+      </c>
+      <c r="E97" t="s">
+        <v>633</v>
+      </c>
+      <c r="F97" t="s">
+        <v>634</v>
+      </c>
+      <c r="G97" s="1">
+        <v>42760</v>
+      </c>
+      <c r="H97">
+        <v>725000</v>
+      </c>
+      <c r="I97" t="s">
+        <v>635</v>
+      </c>
+      <c r="J97" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>637</v>
+      </c>
+      <c r="B98" t="s">
+        <v>638</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>62</v>
+      </c>
+      <c r="E98" t="s">
+        <v>639</v>
+      </c>
+      <c r="F98" t="s">
+        <v>640</v>
+      </c>
+      <c r="G98" s="1">
+        <v>42767</v>
+      </c>
+      <c r="H98">
+        <v>730000</v>
+      </c>
+      <c r="I98" t="s">
+        <v>641</v>
+      </c>
+      <c r="J98" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>643</v>
+      </c>
+      <c r="B99" t="s">
+        <v>644</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" t="s">
+        <v>645</v>
+      </c>
+      <c r="F99" t="s">
+        <v>646</v>
+      </c>
+      <c r="G99" s="1">
+        <v>42774</v>
+      </c>
+      <c r="H99">
+        <v>735000</v>
+      </c>
+      <c r="I99" t="s">
+        <v>647</v>
+      </c>
+      <c r="J99" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>649</v>
+      </c>
+      <c r="B100" t="s">
+        <v>650</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" t="s">
+        <v>77</v>
+      </c>
+      <c r="E100" t="s">
+        <v>651</v>
+      </c>
+      <c r="F100" t="s">
+        <v>652</v>
+      </c>
+      <c r="G100" s="1">
+        <v>42781</v>
+      </c>
+      <c r="H100">
+        <v>740000</v>
+      </c>
+      <c r="I100" t="s">
+        <v>653</v>
+      </c>
+      <c r="J100" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>655</v>
+      </c>
+      <c r="B101" t="s">
+        <v>656</v>
+      </c>
+      <c r="C101" t="s">
+        <v>76</v>
+      </c>
+      <c r="D101" t="s">
+        <v>85</v>
+      </c>
+      <c r="E101" t="s">
+        <v>657</v>
+      </c>
+      <c r="F101" t="s">
+        <v>658</v>
+      </c>
+      <c r="G101" s="1">
+        <v>42788</v>
+      </c>
+      <c r="H101">
+        <v>745000</v>
+      </c>
+      <c r="I101" t="s">
+        <v>659</v>
+      </c>
+      <c r="J101" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>661</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102" t="s">
+        <v>55</v>
+      </c>
+      <c r="E102" t="s">
+        <v>662</v>
+      </c>
+      <c r="F102" t="s">
+        <v>663</v>
+      </c>
+      <c r="G102" s="1">
+        <v>42795</v>
+      </c>
+      <c r="H102">
+        <v>750000</v>
+      </c>
+      <c r="I102" t="s">
+        <v>664</v>
+      </c>
+      <c r="J102" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>666</v>
+      </c>
+      <c r="B103" t="s">
+        <v>61</v>
+      </c>
+      <c r="C103" t="s">
+        <v>92</v>
+      </c>
+      <c r="D103" t="s">
+        <v>62</v>
+      </c>
+      <c r="E103" t="s">
+        <v>667</v>
+      </c>
+      <c r="F103" t="s">
+        <v>668</v>
+      </c>
+      <c r="G103" s="1">
+        <v>42802</v>
+      </c>
+      <c r="H103">
+        <v>755000</v>
+      </c>
+      <c r="I103" t="s">
+        <v>669</v>
+      </c>
+      <c r="J103" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>671</v>
+      </c>
+      <c r="B104" t="s">
+        <v>68</v>
+      </c>
+      <c r="C104" t="s">
+        <v>99</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" t="s">
+        <v>672</v>
+      </c>
+      <c r="F104" t="s">
+        <v>673</v>
+      </c>
+      <c r="G104" s="1">
+        <v>42809</v>
+      </c>
+      <c r="H104">
+        <v>760000</v>
+      </c>
+      <c r="I104" t="s">
+        <v>674</v>
+      </c>
+      <c r="J104" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>676</v>
+      </c>
+      <c r="B105" t="s">
+        <v>75</v>
+      </c>
+      <c r="C105" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" t="s">
+        <v>77</v>
+      </c>
+      <c r="E105" t="s">
+        <v>677</v>
+      </c>
+      <c r="F105" t="s">
+        <v>678</v>
+      </c>
+      <c r="G105" s="1">
+        <v>42816</v>
+      </c>
+      <c r="H105">
+        <v>765000</v>
+      </c>
+      <c r="I105" t="s">
+        <v>679</v>
+      </c>
+      <c r="J105" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>681</v>
+      </c>
+      <c r="B106" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" t="s">
+        <v>85</v>
+      </c>
+      <c r="E106" t="s">
+        <v>682</v>
+      </c>
+      <c r="F106" t="s">
+        <v>683</v>
+      </c>
+      <c r="G106" s="1">
+        <v>42823</v>
+      </c>
+      <c r="H106">
+        <v>770000</v>
+      </c>
+      <c r="I106" t="s">
+        <v>684</v>
+      </c>
+      <c r="J106" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>686</v>
+      </c>
+      <c r="B107" t="s">
+        <v>91</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" t="s">
+        <v>55</v>
+      </c>
+      <c r="E107" t="s">
+        <v>687</v>
+      </c>
+      <c r="F107" t="s">
+        <v>688</v>
+      </c>
+      <c r="G107" s="1">
+        <v>42830</v>
+      </c>
+      <c r="H107">
+        <v>775000</v>
+      </c>
+      <c r="I107" t="s">
+        <v>689</v>
+      </c>
+      <c r="J107" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>691</v>
+      </c>
+      <c r="B108" t="s">
+        <v>98</v>
+      </c>
+      <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" t="s">
+        <v>62</v>
+      </c>
+      <c r="E108" t="s">
+        <v>692</v>
+      </c>
+      <c r="F108" t="s">
+        <v>693</v>
+      </c>
+      <c r="G108" s="1">
+        <v>42837</v>
+      </c>
+      <c r="H108">
+        <v>780000</v>
+      </c>
+      <c r="I108" t="s">
+        <v>694</v>
+      </c>
+      <c r="J108" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>696</v>
+      </c>
+      <c r="B109" t="s">
+        <v>105</v>
+      </c>
+      <c r="C109" t="s">
+        <v>76</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" t="s">
+        <v>697</v>
+      </c>
+      <c r="F109" t="s">
+        <v>698</v>
+      </c>
+      <c r="G109" s="1">
+        <v>42844</v>
+      </c>
+      <c r="H109">
+        <v>785000</v>
+      </c>
+      <c r="I109" t="s">
+        <v>699</v>
+      </c>
+      <c r="J109" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>701</v>
+      </c>
+      <c r="B110" t="s">
+        <v>112</v>
+      </c>
+      <c r="C110" t="s">
+        <v>84</v>
+      </c>
+      <c r="D110" t="s">
+        <v>77</v>
+      </c>
+      <c r="E110" t="s">
+        <v>702</v>
+      </c>
+      <c r="F110" t="s">
+        <v>703</v>
+      </c>
+      <c r="G110" s="1">
+        <v>42851</v>
+      </c>
+      <c r="H110">
+        <v>790000</v>
+      </c>
+      <c r="I110" t="s">
+        <v>704</v>
+      </c>
+      <c r="J110" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>706</v>
+      </c>
+      <c r="B111" t="s">
+        <v>118</v>
+      </c>
+      <c r="C111" t="s">
+        <v>92</v>
+      </c>
+      <c r="D111" t="s">
+        <v>85</v>
+      </c>
+      <c r="E111" t="s">
+        <v>707</v>
+      </c>
+      <c r="F111" t="s">
+        <v>708</v>
+      </c>
+      <c r="G111" s="1">
+        <v>42858</v>
+      </c>
+      <c r="H111">
+        <v>795000</v>
+      </c>
+      <c r="I111" t="s">
+        <v>709</v>
+      </c>
+      <c r="J111" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>711</v>
+      </c>
+      <c r="B112" t="s">
+        <v>124</v>
+      </c>
+      <c r="C112" t="s">
+        <v>99</v>
+      </c>
+      <c r="D112" t="s">
+        <v>55</v>
+      </c>
+      <c r="E112" t="s">
+        <v>712</v>
+      </c>
+      <c r="F112" t="s">
+        <v>713</v>
+      </c>
+      <c r="G112" s="1">
+        <v>42865</v>
+      </c>
+      <c r="H112">
+        <v>800000</v>
+      </c>
+      <c r="I112" t="s">
+        <v>714</v>
+      </c>
+      <c r="J112" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>716</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" t="s">
+        <v>62</v>
+      </c>
+      <c r="E113" t="s">
+        <v>717</v>
+      </c>
+      <c r="F113" t="s">
+        <v>718</v>
+      </c>
+      <c r="G113" s="1">
+        <v>42872</v>
+      </c>
+      <c r="H113">
+        <v>805000</v>
+      </c>
+      <c r="I113" t="s">
+        <v>719</v>
+      </c>
+      <c r="J113" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>721</v>
+      </c>
+      <c r="B114" t="s">
+        <v>135</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" t="s">
+        <v>722</v>
+      </c>
+      <c r="F114" t="s">
+        <v>723</v>
+      </c>
+      <c r="G114" s="1">
+        <v>42879</v>
+      </c>
+      <c r="H114">
+        <v>810000</v>
+      </c>
+      <c r="I114" t="s">
+        <v>724</v>
+      </c>
+      <c r="J114" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>726</v>
+      </c>
+      <c r="B115" t="s">
+        <v>141</v>
+      </c>
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" t="s">
+        <v>77</v>
+      </c>
+      <c r="E115" t="s">
+        <v>727</v>
+      </c>
+      <c r="F115" t="s">
+        <v>728</v>
+      </c>
+      <c r="G115" s="1">
+        <v>42886</v>
+      </c>
+      <c r="H115">
+        <v>815000</v>
+      </c>
+      <c r="I115" t="s">
+        <v>729</v>
+      </c>
+      <c r="J115" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>731</v>
+      </c>
+      <c r="B116" t="s">
+        <v>147</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" t="s">
+        <v>85</v>
+      </c>
+      <c r="E116" t="s">
+        <v>732</v>
+      </c>
+      <c r="F116" t="s">
+        <v>733</v>
+      </c>
+      <c r="G116" s="1">
+        <v>42893</v>
+      </c>
+      <c r="H116">
+        <v>820000</v>
+      </c>
+      <c r="I116" t="s">
+        <v>734</v>
+      </c>
+      <c r="J116" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>736</v>
+      </c>
+      <c r="B117" t="s">
+        <v>153</v>
+      </c>
+      <c r="C117" t="s">
+        <v>76</v>
+      </c>
+      <c r="D117" t="s">
+        <v>55</v>
+      </c>
+      <c r="E117" t="s">
+        <v>737</v>
+      </c>
+      <c r="F117" t="s">
+        <v>738</v>
+      </c>
+      <c r="G117" s="1">
+        <v>42900</v>
+      </c>
+      <c r="H117">
+        <v>825000</v>
+      </c>
+      <c r="I117" t="s">
+        <v>739</v>
+      </c>
+      <c r="J117" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>741</v>
+      </c>
+      <c r="B118" t="s">
+        <v>159</v>
+      </c>
+      <c r="C118" t="s">
+        <v>84</v>
+      </c>
+      <c r="D118" t="s">
+        <v>62</v>
+      </c>
+      <c r="E118" t="s">
+        <v>742</v>
+      </c>
+      <c r="F118" t="s">
+        <v>743</v>
+      </c>
+      <c r="G118" s="1">
+        <v>42907</v>
+      </c>
+      <c r="H118">
+        <v>830000</v>
+      </c>
+      <c r="I118" t="s">
+        <v>744</v>
+      </c>
+      <c r="J118" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>746</v>
+      </c>
+      <c r="B119" t="s">
+        <v>165</v>
+      </c>
+      <c r="C119" t="s">
+        <v>92</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" t="s">
+        <v>747</v>
+      </c>
+      <c r="F119" t="s">
+        <v>748</v>
+      </c>
+      <c r="G119" s="1">
+        <v>42914</v>
+      </c>
+      <c r="H119">
+        <v>835000</v>
+      </c>
+      <c r="I119" t="s">
+        <v>749</v>
+      </c>
+      <c r="J119" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>751</v>
+      </c>
+      <c r="B120" t="s">
+        <v>171</v>
+      </c>
+      <c r="C120" t="s">
+        <v>99</v>
+      </c>
+      <c r="D120" t="s">
+        <v>77</v>
+      </c>
+      <c r="E120" t="s">
+        <v>752</v>
+      </c>
+      <c r="F120" t="s">
+        <v>753</v>
+      </c>
+      <c r="G120" s="1">
+        <v>42921</v>
+      </c>
+      <c r="H120">
+        <v>840000</v>
+      </c>
+      <c r="I120" t="s">
+        <v>754</v>
+      </c>
+      <c r="J120" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>756</v>
+      </c>
+      <c r="B121" t="s">
+        <v>177</v>
+      </c>
+      <c r="C121" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121" t="s">
+        <v>85</v>
+      </c>
+      <c r="E121" t="s">
+        <v>757</v>
+      </c>
+      <c r="F121" t="s">
+        <v>758</v>
+      </c>
+      <c r="G121" s="1">
+        <v>42928</v>
+      </c>
+      <c r="H121">
+        <v>845000</v>
+      </c>
+      <c r="I121" t="s">
+        <v>759</v>
+      </c>
+      <c r="J121" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>761</v>
+      </c>
+      <c r="B122" t="s">
+        <v>183</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>55</v>
+      </c>
+      <c r="E122" t="s">
+        <v>762</v>
+      </c>
+      <c r="F122" t="s">
+        <v>763</v>
+      </c>
+      <c r="G122" s="1">
+        <v>42935</v>
+      </c>
+      <c r="H122">
+        <v>850000</v>
+      </c>
+      <c r="I122" t="s">
+        <v>764</v>
+      </c>
+      <c r="J122" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>766</v>
+      </c>
+      <c r="B123" t="s">
+        <v>189</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>62</v>
+      </c>
+      <c r="E123" t="s">
+        <v>767</v>
+      </c>
+      <c r="F123" t="s">
+        <v>768</v>
+      </c>
+      <c r="G123" s="1">
+        <v>42942</v>
+      </c>
+      <c r="H123">
+        <v>855000</v>
+      </c>
+      <c r="I123" t="s">
+        <v>769</v>
+      </c>
+      <c r="J123" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>771</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" t="s">
+        <v>772</v>
+      </c>
+      <c r="F124" t="s">
+        <v>773</v>
+      </c>
+      <c r="G124" s="1">
+        <v>42949</v>
+      </c>
+      <c r="H124">
+        <v>860000</v>
+      </c>
+      <c r="I124" t="s">
+        <v>774</v>
+      </c>
+      <c r="J124" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>776</v>
+      </c>
+      <c r="B125" t="s">
+        <v>200</v>
+      </c>
+      <c r="C125" t="s">
+        <v>76</v>
+      </c>
+      <c r="D125" t="s">
+        <v>77</v>
+      </c>
+      <c r="E125" t="s">
+        <v>777</v>
+      </c>
+      <c r="F125" t="s">
+        <v>778</v>
+      </c>
+      <c r="G125" s="1">
+        <v>42956</v>
+      </c>
+      <c r="H125">
+        <v>865000</v>
+      </c>
+      <c r="I125" t="s">
+        <v>779</v>
+      </c>
+      <c r="J125" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>781</v>
+      </c>
+      <c r="B126" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" t="s">
+        <v>84</v>
+      </c>
+      <c r="D126" t="s">
+        <v>85</v>
+      </c>
+      <c r="E126" t="s">
+        <v>782</v>
+      </c>
+      <c r="F126" t="s">
+        <v>783</v>
+      </c>
+      <c r="G126" s="1">
+        <v>42963</v>
+      </c>
+      <c r="H126">
+        <v>870000</v>
+      </c>
+      <c r="I126" t="s">
+        <v>784</v>
+      </c>
+      <c r="J126" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>786</v>
+      </c>
+      <c r="B127" t="s">
+        <v>212</v>
+      </c>
+      <c r="C127" t="s">
+        <v>92</v>
+      </c>
+      <c r="D127" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" t="s">
+        <v>787</v>
+      </c>
+      <c r="F127" t="s">
+        <v>788</v>
+      </c>
+      <c r="G127" s="1">
+        <v>42970</v>
+      </c>
+      <c r="H127">
+        <v>875000</v>
+      </c>
+      <c r="I127" t="s">
+        <v>789</v>
+      </c>
+      <c r="J127" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>791</v>
+      </c>
+      <c r="B128" t="s">
+        <v>218</v>
+      </c>
+      <c r="C128" t="s">
+        <v>99</v>
+      </c>
+      <c r="D128" t="s">
+        <v>62</v>
+      </c>
+      <c r="E128" t="s">
+        <v>792</v>
+      </c>
+      <c r="F128" t="s">
+        <v>793</v>
+      </c>
+      <c r="G128" s="1">
+        <v>42977</v>
+      </c>
+      <c r="H128">
+        <v>880000</v>
+      </c>
+      <c r="I128" t="s">
+        <v>794</v>
+      </c>
+      <c r="J128" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>796</v>
+      </c>
+      <c r="B129" t="s">
+        <v>224</v>
+      </c>
+      <c r="C129" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" t="s">
+        <v>797</v>
+      </c>
+      <c r="F129" t="s">
+        <v>798</v>
+      </c>
+      <c r="G129" s="1">
+        <v>42984</v>
+      </c>
+      <c r="H129">
+        <v>885000</v>
+      </c>
+      <c r="I129" t="s">
+        <v>799</v>
+      </c>
+      <c r="J129" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>801</v>
+      </c>
+      <c r="B130" t="s">
+        <v>230</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>77</v>
+      </c>
+      <c r="E130" t="s">
+        <v>802</v>
+      </c>
+      <c r="F130" t="s">
+        <v>803</v>
+      </c>
+      <c r="G130" s="1">
+        <v>42991</v>
+      </c>
+      <c r="H130">
+        <v>890000</v>
+      </c>
+      <c r="I130" t="s">
+        <v>804</v>
+      </c>
+      <c r="J130" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>806</v>
+      </c>
+      <c r="B131" t="s">
+        <v>236</v>
+      </c>
+      <c r="C131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" t="s">
+        <v>85</v>
+      </c>
+      <c r="E131" t="s">
+        <v>807</v>
+      </c>
+      <c r="F131" t="s">
+        <v>808</v>
+      </c>
+      <c r="G131" s="1">
+        <v>42998</v>
+      </c>
+      <c r="H131">
+        <v>895000</v>
+      </c>
+      <c r="I131" t="s">
+        <v>809</v>
+      </c>
+      <c r="J131" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>811</v>
+      </c>
+      <c r="B132" t="s">
+        <v>242</v>
+      </c>
+      <c r="C132" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" t="s">
+        <v>55</v>
+      </c>
+      <c r="E132" t="s">
+        <v>812</v>
+      </c>
+      <c r="F132" t="s">
+        <v>813</v>
+      </c>
+      <c r="G132" s="1">
+        <v>43005</v>
+      </c>
+      <c r="H132">
+        <v>900000</v>
+      </c>
+      <c r="I132" t="s">
+        <v>814</v>
+      </c>
+      <c r="J132" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>816</v>
+      </c>
+      <c r="B133" t="s">
+        <v>248</v>
+      </c>
+      <c r="C133" t="s">
+        <v>76</v>
+      </c>
+      <c r="D133" t="s">
+        <v>62</v>
+      </c>
+      <c r="E133" t="s">
+        <v>817</v>
+      </c>
+      <c r="F133" t="s">
+        <v>818</v>
+      </c>
+      <c r="G133" s="1">
+        <v>43012</v>
+      </c>
+      <c r="H133">
+        <v>905000</v>
+      </c>
+      <c r="I133" t="s">
+        <v>819</v>
+      </c>
+      <c r="J133" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>821</v>
+      </c>
+      <c r="B134" t="s">
+        <v>254</v>
+      </c>
+      <c r="C134" t="s">
+        <v>84</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" t="s">
+        <v>822</v>
+      </c>
+      <c r="F134" t="s">
+        <v>823</v>
+      </c>
+      <c r="G134" s="1">
+        <v>43019</v>
+      </c>
+      <c r="H134">
+        <v>910000</v>
+      </c>
+      <c r="I134" t="s">
+        <v>824</v>
+      </c>
+      <c r="J134" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>826</v>
+      </c>
+      <c r="B135" t="s">
+        <v>260</v>
+      </c>
+      <c r="C135" t="s">
+        <v>92</v>
+      </c>
+      <c r="D135" t="s">
+        <v>77</v>
+      </c>
+      <c r="E135" t="s">
+        <v>827</v>
+      </c>
+      <c r="F135" t="s">
+        <v>828</v>
+      </c>
+      <c r="G135" s="1">
+        <v>43026</v>
+      </c>
+      <c r="H135">
+        <v>915000</v>
+      </c>
+      <c r="I135" t="s">
+        <v>829</v>
+      </c>
+      <c r="J135" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>831</v>
+      </c>
+      <c r="B136" t="s">
+        <v>266</v>
+      </c>
+      <c r="C136" t="s">
+        <v>99</v>
+      </c>
+      <c r="D136" t="s">
+        <v>85</v>
+      </c>
+      <c r="E136" t="s">
+        <v>832</v>
+      </c>
+      <c r="F136" t="s">
+        <v>833</v>
+      </c>
+      <c r="G136" s="1">
+        <v>43033</v>
+      </c>
+      <c r="H136">
+        <v>920000</v>
+      </c>
+      <c r="I136" t="s">
+        <v>834</v>
+      </c>
+      <c r="J136" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>836</v>
+      </c>
+      <c r="B137" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" t="s">
+        <v>55</v>
+      </c>
+      <c r="E137" t="s">
+        <v>837</v>
+      </c>
+      <c r="F137" t="s">
+        <v>838</v>
+      </c>
+      <c r="G137" s="1">
+        <v>43040</v>
+      </c>
+      <c r="H137">
+        <v>925000</v>
+      </c>
+      <c r="I137" t="s">
+        <v>839</v>
+      </c>
+      <c r="J137" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>841</v>
+      </c>
+      <c r="B138" t="s">
+        <v>278</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>62</v>
+      </c>
+      <c r="E138" t="s">
+        <v>842</v>
+      </c>
+      <c r="F138" t="s">
+        <v>843</v>
+      </c>
+      <c r="G138" s="1">
+        <v>43047</v>
+      </c>
+      <c r="H138">
+        <v>930000</v>
+      </c>
+      <c r="I138" t="s">
+        <v>844</v>
+      </c>
+      <c r="J138" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>846</v>
+      </c>
+      <c r="B139" t="s">
+        <v>284</v>
+      </c>
+      <c r="C139" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" t="s">
+        <v>847</v>
+      </c>
+      <c r="F139" t="s">
+        <v>848</v>
+      </c>
+      <c r="G139" s="1">
+        <v>43054</v>
+      </c>
+      <c r="H139">
+        <v>935000</v>
+      </c>
+      <c r="I139" t="s">
+        <v>849</v>
+      </c>
+      <c r="J139" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>851</v>
+      </c>
+      <c r="B140" t="s">
+        <v>290</v>
+      </c>
+      <c r="C140" t="s">
+        <v>13</v>
+      </c>
+      <c r="D140" t="s">
+        <v>77</v>
+      </c>
+      <c r="E140" t="s">
+        <v>852</v>
+      </c>
+      <c r="F140" t="s">
+        <v>853</v>
+      </c>
+      <c r="G140" s="1">
+        <v>43061</v>
+      </c>
+      <c r="H140">
+        <v>940000</v>
+      </c>
+      <c r="I140" t="s">
+        <v>854</v>
+      </c>
+      <c r="J140" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>856</v>
+      </c>
+      <c r="B141" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" t="s">
+        <v>76</v>
+      </c>
+      <c r="D141" t="s">
+        <v>85</v>
+      </c>
+      <c r="E141" t="s">
+        <v>857</v>
+      </c>
+      <c r="F141" t="s">
+        <v>858</v>
+      </c>
+      <c r="G141" s="1">
+        <v>43068</v>
+      </c>
+      <c r="H141">
+        <v>945000</v>
+      </c>
+      <c r="I141" t="s">
+        <v>859</v>
+      </c>
+      <c r="J141" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>861</v>
+      </c>
+      <c r="B142" t="s">
+        <v>302</v>
+      </c>
+      <c r="C142" t="s">
+        <v>84</v>
+      </c>
+      <c r="D142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E142" t="s">
+        <v>862</v>
+      </c>
+      <c r="F142" t="s">
+        <v>863</v>
+      </c>
+      <c r="G142" s="1">
+        <v>43075</v>
+      </c>
+      <c r="H142">
+        <v>950000</v>
+      </c>
+      <c r="I142" t="s">
+        <v>864</v>
+      </c>
+      <c r="J142" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>866</v>
+      </c>
+      <c r="B143" t="s">
+        <v>308</v>
+      </c>
+      <c r="C143" t="s">
+        <v>92</v>
+      </c>
+      <c r="D143" t="s">
+        <v>62</v>
+      </c>
+      <c r="E143" t="s">
+        <v>867</v>
+      </c>
+      <c r="F143" t="s">
+        <v>868</v>
+      </c>
+      <c r="G143" s="1">
+        <v>43082</v>
+      </c>
+      <c r="H143">
+        <v>955000</v>
+      </c>
+      <c r="I143" t="s">
+        <v>869</v>
+      </c>
+      <c r="J143" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>871</v>
+      </c>
+      <c r="B144" t="s">
+        <v>314</v>
+      </c>
+      <c r="C144" t="s">
+        <v>99</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" t="s">
+        <v>872</v>
+      </c>
+      <c r="F144" t="s">
+        <v>873</v>
+      </c>
+      <c r="G144" s="1">
+        <v>43089</v>
+      </c>
+      <c r="H144">
+        <v>960000</v>
+      </c>
+      <c r="I144" t="s">
+        <v>874</v>
+      </c>
+      <c r="J144" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>876</v>
+      </c>
+      <c r="B145" t="s">
+        <v>320</v>
+      </c>
+      <c r="C145" t="s">
+        <v>106</v>
+      </c>
+      <c r="D145" t="s">
+        <v>77</v>
+      </c>
+      <c r="E145" t="s">
+        <v>877</v>
+      </c>
+      <c r="F145" t="s">
+        <v>878</v>
+      </c>
+      <c r="G145" s="1">
+        <v>43096</v>
+      </c>
+      <c r="H145">
+        <v>965000</v>
+      </c>
+      <c r="I145" t="s">
+        <v>879</v>
+      </c>
+      <c r="J145" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>881</v>
+      </c>
+      <c r="B146" t="s">
+        <v>326</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>85</v>
+      </c>
+      <c r="E146" t="s">
+        <v>882</v>
+      </c>
+      <c r="F146" t="s">
+        <v>883</v>
+      </c>
+      <c r="G146" s="1">
+        <v>43103</v>
+      </c>
+      <c r="H146">
+        <v>970000</v>
+      </c>
+      <c r="I146" t="s">
+        <v>884</v>
+      </c>
+      <c r="J146" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>886</v>
+      </c>
+      <c r="B147" t="s">
+        <v>332</v>
+      </c>
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>55</v>
+      </c>
+      <c r="E147" t="s">
+        <v>887</v>
+      </c>
+      <c r="F147" t="s">
+        <v>888</v>
+      </c>
+      <c r="G147" s="1">
+        <v>43110</v>
+      </c>
+      <c r="H147">
+        <v>975000</v>
+      </c>
+      <c r="I147" t="s">
+        <v>889</v>
+      </c>
+      <c r="J147" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>891</v>
+      </c>
+      <c r="B148" t="s">
+        <v>338</v>
+      </c>
+      <c r="C148" t="s">
+        <v>13</v>
+      </c>
+      <c r="D148" t="s">
+        <v>62</v>
+      </c>
+      <c r="E148" t="s">
+        <v>892</v>
+      </c>
+      <c r="F148" t="s">
+        <v>893</v>
+      </c>
+      <c r="G148" s="1">
+        <v>43117</v>
+      </c>
+      <c r="H148">
+        <v>980000</v>
+      </c>
+      <c r="I148" t="s">
+        <v>894</v>
+      </c>
+      <c r="J148" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>896</v>
+      </c>
+      <c r="B149" t="s">
+        <v>344</v>
+      </c>
+      <c r="C149" t="s">
+        <v>76</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" t="s">
+        <v>897</v>
+      </c>
+      <c r="F149" t="s">
+        <v>898</v>
+      </c>
+      <c r="G149" s="1">
+        <v>43124</v>
+      </c>
+      <c r="H149">
+        <v>985000</v>
+      </c>
+      <c r="I149" t="s">
+        <v>899</v>
+      </c>
+      <c r="J149" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>901</v>
+      </c>
+      <c r="B150" t="s">
+        <v>350</v>
+      </c>
+      <c r="C150" t="s">
+        <v>84</v>
+      </c>
+      <c r="D150" t="s">
+        <v>77</v>
+      </c>
+      <c r="E150" t="s">
+        <v>902</v>
+      </c>
+      <c r="F150" t="s">
+        <v>903</v>
+      </c>
+      <c r="G150" s="1">
+        <v>43131</v>
+      </c>
+      <c r="H150">
+        <v>990000</v>
+      </c>
+      <c r="I150" t="s">
+        <v>904</v>
+      </c>
+      <c r="J150" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>906</v>
+      </c>
+      <c r="B151" t="s">
+        <v>356</v>
+      </c>
+      <c r="C151" t="s">
+        <v>92</v>
+      </c>
+      <c r="D151" t="s">
+        <v>85</v>
+      </c>
+      <c r="E151" t="s">
+        <v>907</v>
+      </c>
+      <c r="F151" t="s">
+        <v>908</v>
+      </c>
+      <c r="G151" s="1">
+        <v>43138</v>
+      </c>
+      <c r="H151">
+        <v>995000</v>
+      </c>
+      <c r="I151" t="s">
+        <v>909</v>
+      </c>
+      <c r="J151" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>911</v>
+      </c>
+      <c r="B152" t="s">
+        <v>362</v>
+      </c>
+      <c r="C152" t="s">
+        <v>99</v>
+      </c>
+      <c r="D152" t="s">
+        <v>55</v>
+      </c>
+      <c r="E152" t="s">
+        <v>912</v>
+      </c>
+      <c r="F152" t="s">
+        <v>913</v>
+      </c>
+      <c r="G152" s="1">
+        <v>43145</v>
+      </c>
+      <c r="H152">
+        <v>1000000</v>
+      </c>
+      <c r="I152" t="s">
+        <v>914</v>
+      </c>
+      <c r="J152" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>916</v>
+      </c>
+      <c r="B153" t="s">
+        <v>368</v>
+      </c>
+      <c r="C153" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" t="s">
+        <v>62</v>
+      </c>
+      <c r="E153" t="s">
+        <v>917</v>
+      </c>
+      <c r="F153" t="s">
+        <v>918</v>
+      </c>
+      <c r="G153" s="1">
+        <v>43152</v>
+      </c>
+      <c r="H153">
+        <v>1005000</v>
+      </c>
+      <c r="I153" t="s">
+        <v>919</v>
+      </c>
+      <c r="J153" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>921</v>
+      </c>
+      <c r="B154" t="s">
+        <v>374</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" t="s">
+        <v>922</v>
+      </c>
+      <c r="F154" t="s">
+        <v>923</v>
+      </c>
+      <c r="G154" s="1">
+        <v>43159</v>
+      </c>
+      <c r="H154">
+        <v>1010000</v>
+      </c>
+      <c r="I154" t="s">
+        <v>924</v>
+      </c>
+      <c r="J154" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>926</v>
+      </c>
+      <c r="B155" t="s">
+        <v>380</v>
+      </c>
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>77</v>
+      </c>
+      <c r="E155" t="s">
+        <v>927</v>
+      </c>
+      <c r="F155" t="s">
+        <v>928</v>
+      </c>
+      <c r="G155" s="1">
+        <v>43166</v>
+      </c>
+      <c r="H155">
+        <v>1015000</v>
+      </c>
+      <c r="I155" t="s">
+        <v>929</v>
+      </c>
+      <c r="J155" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>931</v>
+      </c>
+      <c r="B156" t="s">
+        <v>386</v>
+      </c>
+      <c r="C156" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" t="s">
+        <v>85</v>
+      </c>
+      <c r="E156" t="s">
+        <v>932</v>
+      </c>
+      <c r="F156" t="s">
+        <v>933</v>
+      </c>
+      <c r="G156" s="1">
+        <v>43173</v>
+      </c>
+      <c r="H156">
+        <v>1020000</v>
+      </c>
+      <c r="I156" t="s">
+        <v>934</v>
+      </c>
+      <c r="J156" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>936</v>
+      </c>
+      <c r="B157" t="s">
+        <v>392</v>
+      </c>
+      <c r="C157" t="s">
+        <v>76</v>
+      </c>
+      <c r="D157" t="s">
+        <v>55</v>
+      </c>
+      <c r="E157" t="s">
+        <v>937</v>
+      </c>
+      <c r="F157" t="s">
+        <v>938</v>
+      </c>
+      <c r="G157" s="1">
+        <v>43180</v>
+      </c>
+      <c r="H157">
+        <v>1025000</v>
+      </c>
+      <c r="I157" t="s">
+        <v>939</v>
+      </c>
+      <c r="J157" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>941</v>
+      </c>
+      <c r="B158" t="s">
+        <v>398</v>
+      </c>
+      <c r="C158" t="s">
+        <v>84</v>
+      </c>
+      <c r="D158" t="s">
+        <v>62</v>
+      </c>
+      <c r="E158" t="s">
+        <v>942</v>
+      </c>
+      <c r="F158" t="s">
+        <v>943</v>
+      </c>
+      <c r="G158" s="1">
+        <v>43187</v>
+      </c>
+      <c r="H158">
+        <v>1030000</v>
+      </c>
+      <c r="I158" t="s">
+        <v>944</v>
+      </c>
+      <c r="J158" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>946</v>
+      </c>
+      <c r="B159" t="s">
+        <v>404</v>
+      </c>
+      <c r="C159" t="s">
+        <v>92</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" t="s">
+        <v>947</v>
+      </c>
+      <c r="F159" t="s">
+        <v>948</v>
+      </c>
+      <c r="G159" s="1">
+        <v>43194</v>
+      </c>
+      <c r="H159">
+        <v>1035000</v>
+      </c>
+      <c r="I159" t="s">
+        <v>949</v>
+      </c>
+      <c r="J159" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>951</v>
+      </c>
+      <c r="B160" t="s">
+        <v>410</v>
+      </c>
+      <c r="C160" t="s">
+        <v>99</v>
+      </c>
+      <c r="D160" t="s">
+        <v>77</v>
+      </c>
+      <c r="E160" t="s">
+        <v>952</v>
+      </c>
+      <c r="F160" t="s">
+        <v>953</v>
+      </c>
+      <c r="G160" s="1">
+        <v>43201</v>
+      </c>
+      <c r="H160">
+        <v>1040000</v>
+      </c>
+      <c r="I160" t="s">
+        <v>954</v>
+      </c>
+      <c r="J160" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>956</v>
+      </c>
+      <c r="B161" t="s">
+        <v>416</v>
+      </c>
+      <c r="C161" t="s">
+        <v>106</v>
+      </c>
+      <c r="D161" t="s">
+        <v>85</v>
+      </c>
+      <c r="E161" t="s">
+        <v>957</v>
+      </c>
+      <c r="F161" t="s">
+        <v>958</v>
+      </c>
+      <c r="G161" s="1">
+        <v>43208</v>
+      </c>
+      <c r="H161">
+        <v>1045000</v>
+      </c>
+      <c r="I161" t="s">
+        <v>959</v>
+      </c>
+      <c r="J161" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>961</v>
+      </c>
+      <c r="B162" t="s">
+        <v>422</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>55</v>
+      </c>
+      <c r="E162" t="s">
+        <v>962</v>
+      </c>
+      <c r="F162" t="s">
+        <v>963</v>
+      </c>
+      <c r="G162" s="1">
+        <v>43215</v>
+      </c>
+      <c r="H162">
+        <v>1050000</v>
+      </c>
+      <c r="I162" t="s">
+        <v>964</v>
+      </c>
+      <c r="J162" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>966</v>
+      </c>
+      <c r="B163" t="s">
+        <v>428</v>
+      </c>
+      <c r="C163" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" t="s">
+        <v>62</v>
+      </c>
+      <c r="E163" t="s">
+        <v>967</v>
+      </c>
+      <c r="F163" t="s">
+        <v>968</v>
+      </c>
+      <c r="G163" s="1">
+        <v>43222</v>
+      </c>
+      <c r="H163">
+        <v>1055000</v>
+      </c>
+      <c r="I163" t="s">
+        <v>969</v>
+      </c>
+      <c r="J163" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>971</v>
+      </c>
+      <c r="B164" t="s">
+        <v>434</v>
+      </c>
+      <c r="C164" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" t="s">
+        <v>972</v>
+      </c>
+      <c r="F164" t="s">
+        <v>973</v>
+      </c>
+      <c r="G164" s="1">
+        <v>43229</v>
+      </c>
+      <c r="H164">
+        <v>1060000</v>
+      </c>
+      <c r="I164" t="s">
+        <v>974</v>
+      </c>
+      <c r="J164" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>976</v>
+      </c>
+      <c r="B165" t="s">
+        <v>440</v>
+      </c>
+      <c r="C165" t="s">
+        <v>76</v>
+      </c>
+      <c r="D165" t="s">
+        <v>77</v>
+      </c>
+      <c r="E165" t="s">
+        <v>977</v>
+      </c>
+      <c r="F165" t="s">
+        <v>978</v>
+      </c>
+      <c r="G165" s="1">
+        <v>43236</v>
+      </c>
+      <c r="H165">
+        <v>1065000</v>
+      </c>
+      <c r="I165" t="s">
+        <v>979</v>
+      </c>
+      <c r="J165" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>981</v>
+      </c>
+      <c r="B166" t="s">
+        <v>446</v>
+      </c>
+      <c r="C166" t="s">
+        <v>84</v>
+      </c>
+      <c r="D166" t="s">
+        <v>85</v>
+      </c>
+      <c r="E166" t="s">
+        <v>982</v>
+      </c>
+      <c r="F166" t="s">
+        <v>983</v>
+      </c>
+      <c r="G166" s="1">
+        <v>43243</v>
+      </c>
+      <c r="H166">
+        <v>1070000</v>
+      </c>
+      <c r="I166" t="s">
+        <v>984</v>
+      </c>
+      <c r="J166" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>986</v>
+      </c>
+      <c r="B167" t="s">
+        <v>452</v>
+      </c>
+      <c r="C167" t="s">
+        <v>92</v>
+      </c>
+      <c r="D167" t="s">
+        <v>55</v>
+      </c>
+      <c r="E167" t="s">
+        <v>987</v>
+      </c>
+      <c r="F167" t="s">
+        <v>988</v>
+      </c>
+      <c r="G167" s="1">
+        <v>43250</v>
+      </c>
+      <c r="H167">
+        <v>1075000</v>
+      </c>
+      <c r="I167" t="s">
+        <v>989</v>
+      </c>
+      <c r="J167" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>991</v>
+      </c>
+      <c r="B168" t="s">
+        <v>458</v>
+      </c>
+      <c r="C168" t="s">
+        <v>99</v>
+      </c>
+      <c r="D168" t="s">
+        <v>62</v>
+      </c>
+      <c r="E168" t="s">
+        <v>992</v>
+      </c>
+      <c r="F168" t="s">
+        <v>993</v>
+      </c>
+      <c r="G168" s="1">
+        <v>43257</v>
+      </c>
+      <c r="H168">
+        <v>1080000</v>
+      </c>
+      <c r="I168" t="s">
+        <v>994</v>
+      </c>
+      <c r="J168" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A169" t="s">
+        <v>996</v>
+      </c>
+      <c r="B169" t="s">
+        <v>464</v>
+      </c>
+      <c r="C169" t="s">
+        <v>106</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" t="s">
+        <v>997</v>
+      </c>
+      <c r="F169" t="s">
+        <v>998</v>
+      </c>
+      <c r="G169" s="1">
+        <v>43264</v>
+      </c>
+      <c r="H169">
+        <v>1085000</v>
+      </c>
+      <c r="I169" t="s">
+        <v>999</v>
+      </c>
+      <c r="J169" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A170" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B170" t="s">
+        <v>470</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" t="s">
+        <v>77</v>
+      </c>
+      <c r="E170" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F170" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G170" s="1">
+        <v>43271</v>
+      </c>
+      <c r="H170">
+        <v>1090000</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J170" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A171" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B171" t="s">
+        <v>476</v>
+      </c>
+      <c r="C171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" t="s">
+        <v>85</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F171" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G171" s="1">
+        <v>43278</v>
+      </c>
+      <c r="H171">
+        <v>1095000</v>
+      </c>
+      <c r="I171" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J171" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A172" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B172" t="s">
+        <v>482</v>
+      </c>
+      <c r="C172" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" t="s">
+        <v>55</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F172" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G172" s="1">
+        <v>43285</v>
+      </c>
+      <c r="H172">
+        <v>1100000</v>
+      </c>
+      <c r="I172" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J172" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A173" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B173" t="s">
+        <v>488</v>
+      </c>
+      <c r="C173" t="s">
+        <v>76</v>
+      </c>
+      <c r="D173" t="s">
+        <v>62</v>
+      </c>
+      <c r="E173" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F173" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G173" s="1">
+        <v>43292</v>
+      </c>
+      <c r="H173">
+        <v>1105000</v>
+      </c>
+      <c r="I173" t="s">
+        <v>1019</v>
+      </c>
+      <c r="J173" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A174" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B174" t="s">
+        <v>494</v>
+      </c>
+      <c r="C174" t="s">
+        <v>84</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F174" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G174" s="1">
+        <v>43299</v>
+      </c>
+      <c r="H174">
+        <v>1110000</v>
+      </c>
+      <c r="I174" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J174" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A175" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B175" t="s">
+        <v>500</v>
+      </c>
+      <c r="C175" t="s">
+        <v>92</v>
+      </c>
+      <c r="D175" t="s">
+        <v>77</v>
+      </c>
+      <c r="E175" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F175" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G175" s="1">
+        <v>43306</v>
+      </c>
+      <c r="H175">
+        <v>1115000</v>
+      </c>
+      <c r="I175" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A176" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B176" t="s">
+        <v>506</v>
+      </c>
+      <c r="C176" t="s">
+        <v>99</v>
+      </c>
+      <c r="D176" t="s">
+        <v>85</v>
+      </c>
+      <c r="E176" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F176" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G176" s="1">
+        <v>43313</v>
+      </c>
+      <c r="H176">
+        <v>1120000</v>
+      </c>
+      <c r="I176" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J176" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A177" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B177" t="s">
+        <v>512</v>
+      </c>
+      <c r="C177" t="s">
+        <v>106</v>
+      </c>
+      <c r="D177" t="s">
+        <v>55</v>
+      </c>
+      <c r="E177" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F177" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G177" s="1">
+        <v>43320</v>
+      </c>
+      <c r="H177">
+        <v>1125000</v>
+      </c>
+      <c r="I177" t="s">
+        <v>1039</v>
+      </c>
+      <c r="J177" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A178" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B178" t="s">
+        <v>518</v>
+      </c>
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>62</v>
+      </c>
+      <c r="E178" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F178" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G178" s="1">
+        <v>43327</v>
+      </c>
+      <c r="H178">
+        <v>1130000</v>
+      </c>
+      <c r="I178" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J178" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A179" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B179" t="s">
+        <v>524</v>
+      </c>
+      <c r="C179" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F179" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G179" s="1">
+        <v>43334</v>
+      </c>
+      <c r="H179">
+        <v>1135000</v>
+      </c>
+      <c r="I179" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J179" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A180" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B180" t="s">
+        <v>530</v>
+      </c>
+      <c r="C180" t="s">
+        <v>13</v>
+      </c>
+      <c r="D180" t="s">
+        <v>77</v>
+      </c>
+      <c r="E180" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F180" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G180" s="1">
+        <v>43341</v>
+      </c>
+      <c r="H180">
+        <v>1140000</v>
+      </c>
+      <c r="I180" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J180" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A181" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B181" t="s">
+        <v>536</v>
+      </c>
+      <c r="C181" t="s">
+        <v>76</v>
+      </c>
+      <c r="D181" t="s">
+        <v>85</v>
+      </c>
+      <c r="E181" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F181" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G181" s="1">
+        <v>43348</v>
+      </c>
+      <c r="H181">
+        <v>1145000</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J181" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A182" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B182" t="s">
+        <v>542</v>
+      </c>
+      <c r="C182" t="s">
+        <v>84</v>
+      </c>
+      <c r="D182" t="s">
+        <v>55</v>
+      </c>
+      <c r="E182" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F182" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G182" s="1">
+        <v>43355</v>
+      </c>
+      <c r="H182">
+        <v>1150000</v>
+      </c>
+      <c r="I182" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J182" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A183" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B183" t="s">
+        <v>548</v>
+      </c>
+      <c r="C183" t="s">
+        <v>92</v>
+      </c>
+      <c r="D183" t="s">
+        <v>62</v>
+      </c>
+      <c r="E183" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F183" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G183" s="1">
+        <v>43362</v>
+      </c>
+      <c r="H183">
+        <v>1155000</v>
+      </c>
+      <c r="I183" t="s">
+        <v>1069</v>
+      </c>
+      <c r="J183" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A184" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B184" t="s">
+        <v>554</v>
+      </c>
+      <c r="C184" t="s">
+        <v>99</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F184" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G184" s="1">
+        <v>43369</v>
+      </c>
+      <c r="H184">
+        <v>1160000</v>
+      </c>
+      <c r="I184" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J184" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A185" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B185" t="s">
+        <v>560</v>
+      </c>
+      <c r="C185" t="s">
+        <v>106</v>
+      </c>
+      <c r="D185" t="s">
+        <v>77</v>
+      </c>
+      <c r="E185" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F185" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G185" s="1">
+        <v>43376</v>
+      </c>
+      <c r="H185">
+        <v>1165000</v>
+      </c>
+      <c r="I185" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J185" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A186" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B186" t="s">
+        <v>566</v>
+      </c>
+      <c r="C186" t="s">
+        <v>5</v>
+      </c>
+      <c r="D186" t="s">
+        <v>85</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F186" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G186" s="1">
+        <v>43383</v>
+      </c>
+      <c r="H186">
+        <v>1170000</v>
+      </c>
+      <c r="I186" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J186" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A187" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B187" t="s">
+        <v>572</v>
+      </c>
+      <c r="C187" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" t="s">
+        <v>55</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F187" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G187" s="1">
+        <v>43390</v>
+      </c>
+      <c r="H187">
+        <v>1175000</v>
+      </c>
+      <c r="I187" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J187" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A188" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B188" t="s">
+        <v>578</v>
+      </c>
+      <c r="C188" t="s">
+        <v>13</v>
+      </c>
+      <c r="D188" t="s">
+        <v>62</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F188" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G188" s="1">
+        <v>43397</v>
+      </c>
+      <c r="H188">
+        <v>1180000</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J188" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A189" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B189" t="s">
+        <v>584</v>
+      </c>
+      <c r="C189" t="s">
+        <v>76</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F189" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G189" s="1">
+        <v>43404</v>
+      </c>
+      <c r="H189">
+        <v>1185000</v>
+      </c>
+      <c r="I189" t="s">
+        <v>1099</v>
+      </c>
+      <c r="J189" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A190" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B190" t="s">
+        <v>590</v>
+      </c>
+      <c r="C190" t="s">
+        <v>84</v>
+      </c>
+      <c r="D190" t="s">
+        <v>77</v>
+      </c>
+      <c r="E190" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G190" s="1">
+        <v>43411</v>
+      </c>
+      <c r="H190">
+        <v>1190000</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J190" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A191" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B191" t="s">
+        <v>596</v>
+      </c>
+      <c r="C191" t="s">
+        <v>92</v>
+      </c>
+      <c r="D191" t="s">
+        <v>85</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G191" s="1">
+        <v>43418</v>
+      </c>
+      <c r="H191">
+        <v>1195000</v>
+      </c>
+      <c r="I191" t="s">
+        <v>1109</v>
+      </c>
+      <c r="J191" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A192" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B192" t="s">
+        <v>602</v>
+      </c>
+      <c r="C192" t="s">
+        <v>99</v>
+      </c>
+      <c r="D192" t="s">
+        <v>55</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G192" s="1">
+        <v>43425</v>
+      </c>
+      <c r="H192">
+        <v>1200000</v>
+      </c>
+      <c r="I192" t="s">
+        <v>1114</v>
+      </c>
+      <c r="J192" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A193" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B193" t="s">
+        <v>608</v>
+      </c>
+      <c r="C193" t="s">
+        <v>106</v>
+      </c>
+      <c r="D193" t="s">
+        <v>62</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G193" s="1">
+        <v>43432</v>
+      </c>
+      <c r="H193">
+        <v>1205000</v>
+      </c>
+      <c r="I193" t="s">
+        <v>1119</v>
+      </c>
+      <c r="J193" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A194" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B194" t="s">
+        <v>614</v>
+      </c>
+      <c r="C194" t="s">
+        <v>5</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G194" s="1">
+        <v>43439</v>
+      </c>
+      <c r="H194">
+        <v>1210000</v>
+      </c>
+      <c r="I194" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J194" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A195" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B195" t="s">
+        <v>620</v>
+      </c>
+      <c r="C195" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" t="s">
+        <v>77</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G195" s="1">
+        <v>43446</v>
+      </c>
+      <c r="H195">
+        <v>1215000</v>
+      </c>
+      <c r="I195" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J195" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A196" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B196" t="s">
+        <v>626</v>
+      </c>
+      <c r="C196" t="s">
+        <v>13</v>
+      </c>
+      <c r="D196" t="s">
+        <v>85</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G196" s="1">
+        <v>43453</v>
+      </c>
+      <c r="H196">
+        <v>1220000</v>
+      </c>
+      <c r="I196" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J196" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A197" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B197" t="s">
+        <v>632</v>
+      </c>
+      <c r="C197" t="s">
+        <v>76</v>
+      </c>
+      <c r="D197" t="s">
+        <v>55</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G197" s="1">
+        <v>43460</v>
+      </c>
+      <c r="H197">
+        <v>1225000</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1139</v>
+      </c>
+      <c r="J197" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A198" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B198" t="s">
+        <v>638</v>
+      </c>
+      <c r="C198" t="s">
+        <v>84</v>
+      </c>
+      <c r="D198" t="s">
+        <v>62</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G198" s="1">
+        <v>43467</v>
+      </c>
+      <c r="H198">
+        <v>1230000</v>
+      </c>
+      <c r="I198" t="s">
+        <v>1144</v>
+      </c>
+      <c r="J198" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A199" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B199" t="s">
+        <v>644</v>
+      </c>
+      <c r="C199" t="s">
+        <v>92</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G199" s="1">
+        <v>43474</v>
+      </c>
+      <c r="H199">
+        <v>1235000</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J199" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A200" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B200" t="s">
+        <v>650</v>
+      </c>
+      <c r="C200" t="s">
+        <v>99</v>
+      </c>
+      <c r="D200" t="s">
+        <v>77</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G200" s="1">
+        <v>43481</v>
+      </c>
+      <c r="H200">
+        <v>1240000</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A201" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B201" t="s">
+        <v>656</v>
+      </c>
+      <c r="C201" t="s">
+        <v>106</v>
+      </c>
+      <c r="D201" t="s">
+        <v>85</v>
+      </c>
+      <c r="E201" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G201" s="1">
+        <v>43488</v>
+      </c>
+      <c r="H201">
+        <v>1245000</v>
+      </c>
+      <c r="I201" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J201" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>